--- a/planilhas/GRUPO DAS 20 ORIGINALnegativaas para achar no g das 28 as 6 exatas.xlsx
+++ b/planilhas/GRUPO DAS 20 ORIGINALnegativaas para achar no g das 28 as 6 exatas.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2-ANTONIO\GABRIEL 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\SRC\PROJETOS_GIT\desenvolvimento\ws_21\topomanager\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44409070-FC62-40A7-A923-C170926B5D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{E4FEE927-B9FB-4B37-8209-CCC01B2BEDC7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Plan1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1402" uniqueCount="12">
   <si>
     <t>G-1</t>
   </si>
@@ -58,12 +58,70 @@
   <si>
     <t>G-9</t>
   </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>)));</t>
+  </si>
+  <si>
+    <r>
+      <t>negativosDe6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.add(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF7F0055"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>new</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> LinkedHashSet&lt;Integer&gt;(Arrays.</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>asList</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,6 +148,33 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF0000C0"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF7F0055"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -111,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -120,6 +205,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -433,7 +520,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C763B36-43A6-4E09-9E8F-60B79C9857A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:U314"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -9713,4 +9800,8189 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M199"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="61.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="1.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="1.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="1.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="1.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="1.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="1">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1">
+        <v>18</v>
+      </c>
+      <c r="E1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="1">
+        <v>20</v>
+      </c>
+      <c r="G1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="1">
+        <v>21</v>
+      </c>
+      <c r="I1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1">
+        <v>8</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="1">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1">
+        <v>3</v>
+      </c>
+      <c r="K2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="1">
+        <v>14</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="1">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="1">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="1">
+        <v>16</v>
+      </c>
+      <c r="K3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L3" s="1">
+        <v>24</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="1">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="1">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="1">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="1">
+        <v>4</v>
+      </c>
+      <c r="K4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" s="1">
+        <v>23</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="1">
+        <v>21</v>
+      </c>
+      <c r="I5" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="1">
+        <v>15</v>
+      </c>
+      <c r="K5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L5" s="1">
+        <v>19</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="1">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="1">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="1">
+        <v>20</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="1">
+        <v>21</v>
+      </c>
+      <c r="I6" t="s">
+        <v>9</v>
+      </c>
+      <c r="J6" s="1">
+        <v>12</v>
+      </c>
+      <c r="K6" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="1">
+        <v>25</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="1">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="1">
+        <v>20</v>
+      </c>
+      <c r="G7" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="1">
+        <v>21</v>
+      </c>
+      <c r="I7" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="1">
+        <v>9</v>
+      </c>
+      <c r="K7" t="s">
+        <v>9</v>
+      </c>
+      <c r="L7" s="1">
+        <v>10</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="1">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="1">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="1">
+        <v>20</v>
+      </c>
+      <c r="G8" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="1">
+        <v>21</v>
+      </c>
+      <c r="I8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" s="1">
+        <v>5</v>
+      </c>
+      <c r="K8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" s="1">
+        <v>13</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="1">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="1">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="1">
+        <v>20</v>
+      </c>
+      <c r="G9" t="s">
+        <v>9</v>
+      </c>
+      <c r="H9" s="1">
+        <v>21</v>
+      </c>
+      <c r="I9" t="s">
+        <v>9</v>
+      </c>
+      <c r="J9" s="1">
+        <v>12</v>
+      </c>
+      <c r="K9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9" s="1">
+        <v>24</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="1">
+        <v>21</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" s="1">
+        <v>22</v>
+      </c>
+      <c r="I10" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" s="1">
+        <v>7</v>
+      </c>
+      <c r="K10" t="s">
+        <v>9</v>
+      </c>
+      <c r="L10" s="1">
+        <v>8</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="1">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="1">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="1">
+        <v>21</v>
+      </c>
+      <c r="G11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="1">
+        <v>22</v>
+      </c>
+      <c r="I11" t="s">
+        <v>9</v>
+      </c>
+      <c r="J11" s="1">
+        <v>3</v>
+      </c>
+      <c r="K11" t="s">
+        <v>9</v>
+      </c>
+      <c r="L11" s="1">
+        <v>14</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="1">
+        <v>20</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="1">
+        <v>21</v>
+      </c>
+      <c r="G12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="1">
+        <v>22</v>
+      </c>
+      <c r="I12" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="1">
+        <v>16</v>
+      </c>
+      <c r="K12" t="s">
+        <v>9</v>
+      </c>
+      <c r="L12" s="1">
+        <v>24</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1">
+        <v>11</v>
+      </c>
+      <c r="C13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="1">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="1">
+        <v>21</v>
+      </c>
+      <c r="G13" t="s">
+        <v>9</v>
+      </c>
+      <c r="H13" s="1">
+        <v>22</v>
+      </c>
+      <c r="I13" t="s">
+        <v>9</v>
+      </c>
+      <c r="J13" s="1">
+        <v>4</v>
+      </c>
+      <c r="K13" t="s">
+        <v>9</v>
+      </c>
+      <c r="L13" s="1">
+        <v>23</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="1">
+        <v>20</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="1">
+        <v>21</v>
+      </c>
+      <c r="G14" t="s">
+        <v>9</v>
+      </c>
+      <c r="H14" s="1">
+        <v>22</v>
+      </c>
+      <c r="I14" t="s">
+        <v>9</v>
+      </c>
+      <c r="J14" s="1">
+        <v>15</v>
+      </c>
+      <c r="K14" t="s">
+        <v>9</v>
+      </c>
+      <c r="L14" s="1">
+        <v>19</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="1">
+        <v>11</v>
+      </c>
+      <c r="C15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="1">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="1">
+        <v>21</v>
+      </c>
+      <c r="G15" t="s">
+        <v>9</v>
+      </c>
+      <c r="H15" s="1">
+        <v>22</v>
+      </c>
+      <c r="I15" t="s">
+        <v>9</v>
+      </c>
+      <c r="J15" s="1">
+        <v>12</v>
+      </c>
+      <c r="K15" t="s">
+        <v>9</v>
+      </c>
+      <c r="L15" s="1">
+        <v>25</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="1">
+        <v>11</v>
+      </c>
+      <c r="C16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="1">
+        <v>20</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="1">
+        <v>21</v>
+      </c>
+      <c r="G16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H16" s="1">
+        <v>22</v>
+      </c>
+      <c r="I16" t="s">
+        <v>9</v>
+      </c>
+      <c r="J16" s="1">
+        <v>9</v>
+      </c>
+      <c r="K16" t="s">
+        <v>9</v>
+      </c>
+      <c r="L16" s="1">
+        <v>10</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="1">
+        <v>11</v>
+      </c>
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="1">
+        <v>20</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="1">
+        <v>21</v>
+      </c>
+      <c r="G17" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" s="1">
+        <v>22</v>
+      </c>
+      <c r="I17" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="1">
+        <v>5</v>
+      </c>
+      <c r="K17" t="s">
+        <v>9</v>
+      </c>
+      <c r="L17" s="1">
+        <v>13</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="1">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="1">
+        <v>20</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="1">
+        <v>21</v>
+      </c>
+      <c r="G18" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" s="1">
+        <v>22</v>
+      </c>
+      <c r="I18" t="s">
+        <v>9</v>
+      </c>
+      <c r="J18" s="1">
+        <v>17</v>
+      </c>
+      <c r="K18" t="s">
+        <v>9</v>
+      </c>
+      <c r="L18" s="1">
+        <v>18</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="1">
+        <v>11</v>
+      </c>
+      <c r="C19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="1">
+        <v>20</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="1">
+        <v>21</v>
+      </c>
+      <c r="G19" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" s="1">
+        <v>22</v>
+      </c>
+      <c r="I19" t="s">
+        <v>9</v>
+      </c>
+      <c r="J19" s="1">
+        <v>12</v>
+      </c>
+      <c r="K19" t="s">
+        <v>9</v>
+      </c>
+      <c r="L19" s="1">
+        <v>14</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="1">
+        <v>11</v>
+      </c>
+      <c r="C20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="1">
+        <v>17</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="1">
+        <v>21</v>
+      </c>
+      <c r="G20" t="s">
+        <v>9</v>
+      </c>
+      <c r="H20" s="1">
+        <v>22</v>
+      </c>
+      <c r="I20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J20" s="1">
+        <v>7</v>
+      </c>
+      <c r="K20" t="s">
+        <v>9</v>
+      </c>
+      <c r="L20" s="1">
+        <v>8</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="1">
+        <v>11</v>
+      </c>
+      <c r="C21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="1">
+        <v>17</v>
+      </c>
+      <c r="E21" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="1">
+        <v>21</v>
+      </c>
+      <c r="G21" t="s">
+        <v>9</v>
+      </c>
+      <c r="H21" s="1">
+        <v>22</v>
+      </c>
+      <c r="I21" t="s">
+        <v>9</v>
+      </c>
+      <c r="J21" s="1">
+        <v>3</v>
+      </c>
+      <c r="K21" t="s">
+        <v>9</v>
+      </c>
+      <c r="L21" s="1">
+        <v>14</v>
+      </c>
+      <c r="M21" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="1">
+        <v>11</v>
+      </c>
+      <c r="C22" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="1">
+        <v>17</v>
+      </c>
+      <c r="E22" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="1">
+        <v>21</v>
+      </c>
+      <c r="G22" t="s">
+        <v>9</v>
+      </c>
+      <c r="H22" s="1">
+        <v>22</v>
+      </c>
+      <c r="I22" t="s">
+        <v>9</v>
+      </c>
+      <c r="J22" s="1">
+        <v>16</v>
+      </c>
+      <c r="K22" t="s">
+        <v>9</v>
+      </c>
+      <c r="L22" s="1">
+        <v>24</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="1">
+        <v>11</v>
+      </c>
+      <c r="C23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="1">
+        <v>17</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="1">
+        <v>21</v>
+      </c>
+      <c r="G23" t="s">
+        <v>9</v>
+      </c>
+      <c r="H23" s="1">
+        <v>22</v>
+      </c>
+      <c r="I23" t="s">
+        <v>9</v>
+      </c>
+      <c r="J23" s="1">
+        <v>13</v>
+      </c>
+      <c r="K23" t="s">
+        <v>9</v>
+      </c>
+      <c r="L23" s="1">
+        <v>20</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24" s="1">
+        <v>11</v>
+      </c>
+      <c r="C24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="1">
+        <v>17</v>
+      </c>
+      <c r="E24" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="1">
+        <v>21</v>
+      </c>
+      <c r="G24" t="s">
+        <v>9</v>
+      </c>
+      <c r="H24" s="1">
+        <v>22</v>
+      </c>
+      <c r="I24" t="s">
+        <v>9</v>
+      </c>
+      <c r="J24" s="1">
+        <v>4</v>
+      </c>
+      <c r="K24" t="s">
+        <v>9</v>
+      </c>
+      <c r="L24" s="1">
+        <v>23</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25" s="1">
+        <v>11</v>
+      </c>
+      <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="1">
+        <v>17</v>
+      </c>
+      <c r="E25" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="1">
+        <v>21</v>
+      </c>
+      <c r="G25" t="s">
+        <v>9</v>
+      </c>
+      <c r="H25" s="1">
+        <v>22</v>
+      </c>
+      <c r="I25" t="s">
+        <v>9</v>
+      </c>
+      <c r="J25" s="1">
+        <v>15</v>
+      </c>
+      <c r="K25" t="s">
+        <v>9</v>
+      </c>
+      <c r="L25" s="1">
+        <v>19</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="1">
+        <v>11</v>
+      </c>
+      <c r="C26" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="1">
+        <v>17</v>
+      </c>
+      <c r="E26" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="1">
+        <v>21</v>
+      </c>
+      <c r="G26" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="1">
+        <v>22</v>
+      </c>
+      <c r="I26" t="s">
+        <v>9</v>
+      </c>
+      <c r="J26" s="1">
+        <v>12</v>
+      </c>
+      <c r="K26" t="s">
+        <v>9</v>
+      </c>
+      <c r="L26" s="1">
+        <v>25</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="1">
+        <v>11</v>
+      </c>
+      <c r="C27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="1">
+        <v>17</v>
+      </c>
+      <c r="E27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="1">
+        <v>21</v>
+      </c>
+      <c r="G27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="1">
+        <v>22</v>
+      </c>
+      <c r="I27" t="s">
+        <v>9</v>
+      </c>
+      <c r="J27" s="1">
+        <v>9</v>
+      </c>
+      <c r="K27" t="s">
+        <v>9</v>
+      </c>
+      <c r="L27" s="1">
+        <v>10</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="1">
+        <v>11</v>
+      </c>
+      <c r="C28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="1">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="1">
+        <v>21</v>
+      </c>
+      <c r="G28" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" s="1">
+        <v>22</v>
+      </c>
+      <c r="I28" t="s">
+        <v>9</v>
+      </c>
+      <c r="J28" s="1">
+        <v>5</v>
+      </c>
+      <c r="K28" t="s">
+        <v>9</v>
+      </c>
+      <c r="L28" s="1">
+        <v>13</v>
+      </c>
+      <c r="M28" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="1">
+        <v>11</v>
+      </c>
+      <c r="C29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="1">
+        <v>17</v>
+      </c>
+      <c r="E29" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="1">
+        <v>21</v>
+      </c>
+      <c r="G29" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="1">
+        <v>22</v>
+      </c>
+      <c r="I29" t="s">
+        <v>9</v>
+      </c>
+      <c r="J29" s="1">
+        <v>12</v>
+      </c>
+      <c r="K29" t="s">
+        <v>9</v>
+      </c>
+      <c r="L29" s="1">
+        <v>24</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="1">
+        <v>8</v>
+      </c>
+      <c r="C30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="1">
+        <v>10</v>
+      </c>
+      <c r="E30" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="1">
+        <v>14</v>
+      </c>
+      <c r="G30" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="1">
+        <v>25</v>
+      </c>
+      <c r="I30" t="s">
+        <v>9</v>
+      </c>
+      <c r="J30" s="1">
+        <v>18</v>
+      </c>
+      <c r="K30" t="s">
+        <v>9</v>
+      </c>
+      <c r="L30" s="1">
+        <v>22</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="1">
+        <v>8</v>
+      </c>
+      <c r="C31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="1">
+        <v>10</v>
+      </c>
+      <c r="E31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="1">
+        <v>14</v>
+      </c>
+      <c r="G31" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31" s="1">
+        <v>25</v>
+      </c>
+      <c r="I31" t="s">
+        <v>9</v>
+      </c>
+      <c r="J31" s="1">
+        <v>16</v>
+      </c>
+      <c r="K31" t="s">
+        <v>9</v>
+      </c>
+      <c r="L31" s="1">
+        <v>24</v>
+      </c>
+      <c r="M31" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" s="1">
+        <v>8</v>
+      </c>
+      <c r="C32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="1">
+        <v>10</v>
+      </c>
+      <c r="E32" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="1">
+        <v>14</v>
+      </c>
+      <c r="G32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" s="1">
+        <v>25</v>
+      </c>
+      <c r="I32" t="s">
+        <v>9</v>
+      </c>
+      <c r="J32" s="1">
+        <v>13</v>
+      </c>
+      <c r="K32" t="s">
+        <v>9</v>
+      </c>
+      <c r="L32" s="1">
+        <v>20</v>
+      </c>
+      <c r="M32" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" s="1">
+        <v>8</v>
+      </c>
+      <c r="C33" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="1">
+        <v>10</v>
+      </c>
+      <c r="E33" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="1">
+        <v>14</v>
+      </c>
+      <c r="G33" t="s">
+        <v>9</v>
+      </c>
+      <c r="H33" s="1">
+        <v>25</v>
+      </c>
+      <c r="I33" t="s">
+        <v>9</v>
+      </c>
+      <c r="J33" s="1">
+        <v>4</v>
+      </c>
+      <c r="K33" t="s">
+        <v>9</v>
+      </c>
+      <c r="L33" s="1">
+        <v>23</v>
+      </c>
+      <c r="M33" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" s="1">
+        <v>8</v>
+      </c>
+      <c r="C34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="1">
+        <v>10</v>
+      </c>
+      <c r="E34" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="1">
+        <v>14</v>
+      </c>
+      <c r="G34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H34" s="1">
+        <v>25</v>
+      </c>
+      <c r="I34" t="s">
+        <v>9</v>
+      </c>
+      <c r="J34" s="1">
+        <v>15</v>
+      </c>
+      <c r="K34" t="s">
+        <v>9</v>
+      </c>
+      <c r="L34" s="1">
+        <v>19</v>
+      </c>
+      <c r="M34" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" s="1">
+        <v>8</v>
+      </c>
+      <c r="C35" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="1">
+        <v>10</v>
+      </c>
+      <c r="E35" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="1">
+        <v>14</v>
+      </c>
+      <c r="G35" t="s">
+        <v>9</v>
+      </c>
+      <c r="H35" s="1">
+        <v>25</v>
+      </c>
+      <c r="I35" t="s">
+        <v>9</v>
+      </c>
+      <c r="J35" s="1">
+        <v>11</v>
+      </c>
+      <c r="K35" t="s">
+        <v>9</v>
+      </c>
+      <c r="L35" s="1">
+        <v>20</v>
+      </c>
+      <c r="M35" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="1">
+        <v>8</v>
+      </c>
+      <c r="C36" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="1">
+        <v>10</v>
+      </c>
+      <c r="E36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="1">
+        <v>14</v>
+      </c>
+      <c r="G36" t="s">
+        <v>9</v>
+      </c>
+      <c r="H36" s="1">
+        <v>25</v>
+      </c>
+      <c r="I36" t="s">
+        <v>9</v>
+      </c>
+      <c r="J36" s="1">
+        <v>2</v>
+      </c>
+      <c r="K36" t="s">
+        <v>9</v>
+      </c>
+      <c r="L36" s="1">
+        <v>21</v>
+      </c>
+      <c r="M36" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" s="1">
+        <v>8</v>
+      </c>
+      <c r="C37" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="1">
+        <v>10</v>
+      </c>
+      <c r="E37" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="1">
+        <v>14</v>
+      </c>
+      <c r="G37" t="s">
+        <v>9</v>
+      </c>
+      <c r="H37" s="1">
+        <v>25</v>
+      </c>
+      <c r="I37" t="s">
+        <v>9</v>
+      </c>
+      <c r="J37" s="1">
+        <v>5</v>
+      </c>
+      <c r="K37" t="s">
+        <v>9</v>
+      </c>
+      <c r="L37" s="1">
+        <v>13</v>
+      </c>
+      <c r="M37" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" s="1">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="1">
+        <v>10</v>
+      </c>
+      <c r="E38" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="1">
+        <v>14</v>
+      </c>
+      <c r="G38" t="s">
+        <v>9</v>
+      </c>
+      <c r="H38" s="1">
+        <v>25</v>
+      </c>
+      <c r="I38" t="s">
+        <v>9</v>
+      </c>
+      <c r="J38" s="1">
+        <v>17</v>
+      </c>
+      <c r="K38" t="s">
+        <v>9</v>
+      </c>
+      <c r="L38" s="1">
+        <v>18</v>
+      </c>
+      <c r="M38" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" s="1">
+        <v>8</v>
+      </c>
+      <c r="C39" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="1">
+        <v>10</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="1">
+        <v>14</v>
+      </c>
+      <c r="G39" t="s">
+        <v>9</v>
+      </c>
+      <c r="H39" s="1">
+        <v>25</v>
+      </c>
+      <c r="I39" t="s">
+        <v>9</v>
+      </c>
+      <c r="J39" s="1">
+        <v>12</v>
+      </c>
+      <c r="K39" t="s">
+        <v>9</v>
+      </c>
+      <c r="L39" s="1">
+        <v>24</v>
+      </c>
+      <c r="M39" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" s="1">
+        <v>7</v>
+      </c>
+      <c r="C40" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="1">
+        <v>12</v>
+      </c>
+      <c r="E40" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" s="1">
+        <v>16</v>
+      </c>
+      <c r="G40" t="s">
+        <v>9</v>
+      </c>
+      <c r="H40" s="1">
+        <v>25</v>
+      </c>
+      <c r="I40" t="s">
+        <v>9</v>
+      </c>
+      <c r="J40" s="1">
+        <v>3</v>
+      </c>
+      <c r="K40" t="s">
+        <v>9</v>
+      </c>
+      <c r="L40" s="1">
+        <v>4</v>
+      </c>
+      <c r="M40" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" s="1">
+        <v>7</v>
+      </c>
+      <c r="C41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="1">
+        <v>12</v>
+      </c>
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="1">
+        <v>16</v>
+      </c>
+      <c r="G41" t="s">
+        <v>9</v>
+      </c>
+      <c r="H41" s="1">
+        <v>25</v>
+      </c>
+      <c r="I41" t="s">
+        <v>9</v>
+      </c>
+      <c r="J41" s="1">
+        <v>18</v>
+      </c>
+      <c r="K41" t="s">
+        <v>9</v>
+      </c>
+      <c r="L41" s="1">
+        <v>22</v>
+      </c>
+      <c r="M41" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42" s="1">
+        <v>7</v>
+      </c>
+      <c r="C42" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="1">
+        <v>12</v>
+      </c>
+      <c r="E42" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="1">
+        <v>16</v>
+      </c>
+      <c r="G42" t="s">
+        <v>9</v>
+      </c>
+      <c r="H42" s="1">
+        <v>25</v>
+      </c>
+      <c r="I42" t="s">
+        <v>9</v>
+      </c>
+      <c r="J42" s="1">
+        <v>13</v>
+      </c>
+      <c r="K42" t="s">
+        <v>9</v>
+      </c>
+      <c r="L42" s="1">
+        <v>20</v>
+      </c>
+      <c r="M42" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43" s="1">
+        <v>7</v>
+      </c>
+      <c r="C43" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="1">
+        <v>12</v>
+      </c>
+      <c r="E43" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" s="1">
+        <v>16</v>
+      </c>
+      <c r="G43" t="s">
+        <v>9</v>
+      </c>
+      <c r="H43" s="1">
+        <v>25</v>
+      </c>
+      <c r="I43" t="s">
+        <v>9</v>
+      </c>
+      <c r="J43" s="1">
+        <v>4</v>
+      </c>
+      <c r="K43" t="s">
+        <v>9</v>
+      </c>
+      <c r="L43" s="1">
+        <v>23</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44" s="1">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="1">
+        <v>12</v>
+      </c>
+      <c r="E44" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" s="1">
+        <v>16</v>
+      </c>
+      <c r="G44" t="s">
+        <v>9</v>
+      </c>
+      <c r="H44" s="1">
+        <v>25</v>
+      </c>
+      <c r="I44" t="s">
+        <v>9</v>
+      </c>
+      <c r="J44" s="1">
+        <v>15</v>
+      </c>
+      <c r="K44" t="s">
+        <v>9</v>
+      </c>
+      <c r="L44" s="1">
+        <v>19</v>
+      </c>
+      <c r="M44" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45" s="1">
+        <v>7</v>
+      </c>
+      <c r="C45" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="1">
+        <v>12</v>
+      </c>
+      <c r="E45" t="s">
+        <v>9</v>
+      </c>
+      <c r="F45" s="1">
+        <v>16</v>
+      </c>
+      <c r="G45" t="s">
+        <v>9</v>
+      </c>
+      <c r="H45" s="1">
+        <v>25</v>
+      </c>
+      <c r="I45" t="s">
+        <v>9</v>
+      </c>
+      <c r="J45" s="1">
+        <v>9</v>
+      </c>
+      <c r="K45" t="s">
+        <v>9</v>
+      </c>
+      <c r="L45" s="1">
+        <v>10</v>
+      </c>
+      <c r="M45" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" s="1">
+        <v>7</v>
+      </c>
+      <c r="C46" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="1">
+        <v>12</v>
+      </c>
+      <c r="E46" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46" s="1">
+        <v>16</v>
+      </c>
+      <c r="G46" t="s">
+        <v>9</v>
+      </c>
+      <c r="H46" s="1">
+        <v>25</v>
+      </c>
+      <c r="I46" t="s">
+        <v>9</v>
+      </c>
+      <c r="J46" s="1">
+        <v>11</v>
+      </c>
+      <c r="K46" t="s">
+        <v>9</v>
+      </c>
+      <c r="L46" s="1">
+        <v>20</v>
+      </c>
+      <c r="M46" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47" s="1">
+        <v>7</v>
+      </c>
+      <c r="C47" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="1">
+        <v>12</v>
+      </c>
+      <c r="E47" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" s="1">
+        <v>16</v>
+      </c>
+      <c r="G47" t="s">
+        <v>9</v>
+      </c>
+      <c r="H47" s="1">
+        <v>25</v>
+      </c>
+      <c r="I47" t="s">
+        <v>9</v>
+      </c>
+      <c r="J47" s="1">
+        <v>2</v>
+      </c>
+      <c r="K47" t="s">
+        <v>9</v>
+      </c>
+      <c r="L47" s="1">
+        <v>21</v>
+      </c>
+      <c r="M47" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48" s="1">
+        <v>7</v>
+      </c>
+      <c r="C48" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="1">
+        <v>12</v>
+      </c>
+      <c r="E48" t="s">
+        <v>9</v>
+      </c>
+      <c r="F48" s="1">
+        <v>16</v>
+      </c>
+      <c r="G48" t="s">
+        <v>9</v>
+      </c>
+      <c r="H48" s="1">
+        <v>25</v>
+      </c>
+      <c r="I48" t="s">
+        <v>9</v>
+      </c>
+      <c r="J48" s="1">
+        <v>5</v>
+      </c>
+      <c r="K48" t="s">
+        <v>9</v>
+      </c>
+      <c r="L48" s="1">
+        <v>13</v>
+      </c>
+      <c r="M48" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49" s="1">
+        <v>7</v>
+      </c>
+      <c r="C49" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="1">
+        <v>12</v>
+      </c>
+      <c r="E49" t="s">
+        <v>9</v>
+      </c>
+      <c r="F49" s="1">
+        <v>16</v>
+      </c>
+      <c r="G49" t="s">
+        <v>9</v>
+      </c>
+      <c r="H49" s="1">
+        <v>25</v>
+      </c>
+      <c r="I49" t="s">
+        <v>9</v>
+      </c>
+      <c r="J49" s="1">
+        <v>17</v>
+      </c>
+      <c r="K49" t="s">
+        <v>9</v>
+      </c>
+      <c r="L49" s="1">
+        <v>18</v>
+      </c>
+      <c r="M49" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50" s="1">
+        <v>7</v>
+      </c>
+      <c r="C50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="1">
+        <v>10</v>
+      </c>
+      <c r="E50" t="s">
+        <v>9</v>
+      </c>
+      <c r="F50" s="1">
+        <v>13</v>
+      </c>
+      <c r="G50" t="s">
+        <v>9</v>
+      </c>
+      <c r="H50" s="1">
+        <v>15</v>
+      </c>
+      <c r="I50" t="s">
+        <v>9</v>
+      </c>
+      <c r="J50" s="1">
+        <v>3</v>
+      </c>
+      <c r="K50" t="s">
+        <v>9</v>
+      </c>
+      <c r="L50" s="1">
+        <v>14</v>
+      </c>
+      <c r="M50" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51" s="1">
+        <v>7</v>
+      </c>
+      <c r="C51" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="1">
+        <v>10</v>
+      </c>
+      <c r="E51" t="s">
+        <v>9</v>
+      </c>
+      <c r="F51" s="1">
+        <v>13</v>
+      </c>
+      <c r="G51" t="s">
+        <v>9</v>
+      </c>
+      <c r="H51" s="1">
+        <v>15</v>
+      </c>
+      <c r="I51" t="s">
+        <v>9</v>
+      </c>
+      <c r="J51" s="1">
+        <v>18</v>
+      </c>
+      <c r="K51" t="s">
+        <v>9</v>
+      </c>
+      <c r="L51" s="1">
+        <v>22</v>
+      </c>
+      <c r="M51" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" s="1">
+        <v>7</v>
+      </c>
+      <c r="C52" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="1">
+        <v>10</v>
+      </c>
+      <c r="E52" t="s">
+        <v>9</v>
+      </c>
+      <c r="F52" s="1">
+        <v>13</v>
+      </c>
+      <c r="G52" t="s">
+        <v>9</v>
+      </c>
+      <c r="H52" s="1">
+        <v>15</v>
+      </c>
+      <c r="I52" t="s">
+        <v>9</v>
+      </c>
+      <c r="J52" s="1">
+        <v>16</v>
+      </c>
+      <c r="K52" t="s">
+        <v>9</v>
+      </c>
+      <c r="L52" s="1">
+        <v>24</v>
+      </c>
+      <c r="M52" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53" s="1">
+        <v>7</v>
+      </c>
+      <c r="C53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="1">
+        <v>10</v>
+      </c>
+      <c r="E53" t="s">
+        <v>9</v>
+      </c>
+      <c r="F53" s="1">
+        <v>13</v>
+      </c>
+      <c r="G53" t="s">
+        <v>9</v>
+      </c>
+      <c r="H53" s="1">
+        <v>15</v>
+      </c>
+      <c r="I53" t="s">
+        <v>9</v>
+      </c>
+      <c r="J53" s="1">
+        <v>4</v>
+      </c>
+      <c r="K53" t="s">
+        <v>9</v>
+      </c>
+      <c r="L53" s="1">
+        <v>23</v>
+      </c>
+      <c r="M53" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54" s="1">
+        <v>7</v>
+      </c>
+      <c r="C54" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="1">
+        <v>10</v>
+      </c>
+      <c r="E54" t="s">
+        <v>9</v>
+      </c>
+      <c r="F54" s="1">
+        <v>13</v>
+      </c>
+      <c r="G54" t="s">
+        <v>9</v>
+      </c>
+      <c r="H54" s="1">
+        <v>15</v>
+      </c>
+      <c r="I54" t="s">
+        <v>9</v>
+      </c>
+      <c r="J54" s="1">
+        <v>12</v>
+      </c>
+      <c r="K54" t="s">
+        <v>9</v>
+      </c>
+      <c r="L54" s="1">
+        <v>25</v>
+      </c>
+      <c r="M54" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B55" s="1">
+        <v>7</v>
+      </c>
+      <c r="C55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="1">
+        <v>10</v>
+      </c>
+      <c r="E55" t="s">
+        <v>9</v>
+      </c>
+      <c r="F55" s="1">
+        <v>13</v>
+      </c>
+      <c r="G55" t="s">
+        <v>9</v>
+      </c>
+      <c r="H55" s="1">
+        <v>15</v>
+      </c>
+      <c r="I55" t="s">
+        <v>9</v>
+      </c>
+      <c r="J55" s="1">
+        <v>11</v>
+      </c>
+      <c r="K55" t="s">
+        <v>9</v>
+      </c>
+      <c r="L55" s="1">
+        <v>20</v>
+      </c>
+      <c r="M55" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56" s="1">
+        <v>7</v>
+      </c>
+      <c r="C56" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="1">
+        <v>10</v>
+      </c>
+      <c r="E56" t="s">
+        <v>9</v>
+      </c>
+      <c r="F56" s="1">
+        <v>13</v>
+      </c>
+      <c r="G56" t="s">
+        <v>9</v>
+      </c>
+      <c r="H56" s="1">
+        <v>15</v>
+      </c>
+      <c r="I56" t="s">
+        <v>9</v>
+      </c>
+      <c r="J56" s="1">
+        <v>2</v>
+      </c>
+      <c r="K56" t="s">
+        <v>9</v>
+      </c>
+      <c r="L56" s="1">
+        <v>21</v>
+      </c>
+      <c r="M56" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" s="1">
+        <v>7</v>
+      </c>
+      <c r="C57" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="1">
+        <v>10</v>
+      </c>
+      <c r="E57" t="s">
+        <v>9</v>
+      </c>
+      <c r="F57" s="1">
+        <v>13</v>
+      </c>
+      <c r="G57" t="s">
+        <v>9</v>
+      </c>
+      <c r="H57" s="1">
+        <v>15</v>
+      </c>
+      <c r="I57" t="s">
+        <v>9</v>
+      </c>
+      <c r="J57" s="1">
+        <v>17</v>
+      </c>
+      <c r="K57" t="s">
+        <v>9</v>
+      </c>
+      <c r="L57" s="1">
+        <v>18</v>
+      </c>
+      <c r="M57" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" s="1">
+        <v>7</v>
+      </c>
+      <c r="C58" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="1">
+        <v>10</v>
+      </c>
+      <c r="E58" t="s">
+        <v>9</v>
+      </c>
+      <c r="F58" s="1">
+        <v>13</v>
+      </c>
+      <c r="G58" t="s">
+        <v>9</v>
+      </c>
+      <c r="H58" s="1">
+        <v>15</v>
+      </c>
+      <c r="I58" t="s">
+        <v>9</v>
+      </c>
+      <c r="J58" s="1">
+        <v>12</v>
+      </c>
+      <c r="K58" t="s">
+        <v>9</v>
+      </c>
+      <c r="L58" s="1">
+        <v>24</v>
+      </c>
+      <c r="M58" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59" s="1">
+        <v>6</v>
+      </c>
+      <c r="C59" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="1">
+        <v>9</v>
+      </c>
+      <c r="E59" t="s">
+        <v>9</v>
+      </c>
+      <c r="F59" s="1">
+        <v>19</v>
+      </c>
+      <c r="G59" t="s">
+        <v>9</v>
+      </c>
+      <c r="H59" s="1">
+        <v>24</v>
+      </c>
+      <c r="I59" t="s">
+        <v>9</v>
+      </c>
+      <c r="J59" s="1">
+        <v>7</v>
+      </c>
+      <c r="K59" t="s">
+        <v>9</v>
+      </c>
+      <c r="L59" s="1">
+        <v>8</v>
+      </c>
+      <c r="M59" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60" s="1">
+        <v>6</v>
+      </c>
+      <c r="C60" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="1">
+        <v>9</v>
+      </c>
+      <c r="E60" t="s">
+        <v>9</v>
+      </c>
+      <c r="F60" s="1">
+        <v>19</v>
+      </c>
+      <c r="G60" t="s">
+        <v>9</v>
+      </c>
+      <c r="H60" s="1">
+        <v>24</v>
+      </c>
+      <c r="I60" t="s">
+        <v>9</v>
+      </c>
+      <c r="J60" s="1">
+        <v>3</v>
+      </c>
+      <c r="K60" t="s">
+        <v>9</v>
+      </c>
+      <c r="L60" s="1">
+        <v>14</v>
+      </c>
+      <c r="M60" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B61" s="1">
+        <v>6</v>
+      </c>
+      <c r="C61" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" s="1">
+        <v>9</v>
+      </c>
+      <c r="E61" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61" s="1">
+        <v>19</v>
+      </c>
+      <c r="G61" t="s">
+        <v>9</v>
+      </c>
+      <c r="H61" s="1">
+        <v>24</v>
+      </c>
+      <c r="I61" t="s">
+        <v>9</v>
+      </c>
+      <c r="J61" s="1">
+        <v>18</v>
+      </c>
+      <c r="K61" t="s">
+        <v>9</v>
+      </c>
+      <c r="L61" s="1">
+        <v>22</v>
+      </c>
+      <c r="M61" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62" s="1">
+        <v>6</v>
+      </c>
+      <c r="C62" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" s="1">
+        <v>9</v>
+      </c>
+      <c r="E62" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62" s="1">
+        <v>19</v>
+      </c>
+      <c r="G62" t="s">
+        <v>9</v>
+      </c>
+      <c r="H62" s="1">
+        <v>24</v>
+      </c>
+      <c r="I62" t="s">
+        <v>9</v>
+      </c>
+      <c r="J62" s="1">
+        <v>13</v>
+      </c>
+      <c r="K62" t="s">
+        <v>9</v>
+      </c>
+      <c r="L62" s="1">
+        <v>20</v>
+      </c>
+      <c r="M62" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" s="1">
+        <v>6</v>
+      </c>
+      <c r="C63" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="1">
+        <v>9</v>
+      </c>
+      <c r="E63" t="s">
+        <v>9</v>
+      </c>
+      <c r="F63" s="1">
+        <v>19</v>
+      </c>
+      <c r="G63" t="s">
+        <v>9</v>
+      </c>
+      <c r="H63" s="1">
+        <v>24</v>
+      </c>
+      <c r="I63" t="s">
+        <v>9</v>
+      </c>
+      <c r="J63" s="1">
+        <v>4</v>
+      </c>
+      <c r="K63" t="s">
+        <v>9</v>
+      </c>
+      <c r="L63" s="1">
+        <v>23</v>
+      </c>
+      <c r="M63" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B64" s="1">
+        <v>6</v>
+      </c>
+      <c r="C64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" s="1">
+        <v>9</v>
+      </c>
+      <c r="E64" t="s">
+        <v>9</v>
+      </c>
+      <c r="F64" s="1">
+        <v>19</v>
+      </c>
+      <c r="G64" t="s">
+        <v>9</v>
+      </c>
+      <c r="H64" s="1">
+        <v>24</v>
+      </c>
+      <c r="I64" t="s">
+        <v>9</v>
+      </c>
+      <c r="J64" s="1">
+        <v>12</v>
+      </c>
+      <c r="K64" t="s">
+        <v>9</v>
+      </c>
+      <c r="L64" s="1">
+        <v>25</v>
+      </c>
+      <c r="M64" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" s="1">
+        <v>6</v>
+      </c>
+      <c r="C65" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="1">
+        <v>9</v>
+      </c>
+      <c r="E65" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65" s="1">
+        <v>19</v>
+      </c>
+      <c r="G65" t="s">
+        <v>9</v>
+      </c>
+      <c r="H65" s="1">
+        <v>24</v>
+      </c>
+      <c r="I65" t="s">
+        <v>9</v>
+      </c>
+      <c r="J65" s="1">
+        <v>11</v>
+      </c>
+      <c r="K65" t="s">
+        <v>9</v>
+      </c>
+      <c r="L65" s="1">
+        <v>20</v>
+      </c>
+      <c r="M65" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66" s="1">
+        <v>6</v>
+      </c>
+      <c r="C66" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="1">
+        <v>9</v>
+      </c>
+      <c r="E66" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66" s="1">
+        <v>19</v>
+      </c>
+      <c r="G66" t="s">
+        <v>9</v>
+      </c>
+      <c r="H66" s="1">
+        <v>24</v>
+      </c>
+      <c r="I66" t="s">
+        <v>9</v>
+      </c>
+      <c r="J66" s="1">
+        <v>2</v>
+      </c>
+      <c r="K66" t="s">
+        <v>9</v>
+      </c>
+      <c r="L66" s="1">
+        <v>21</v>
+      </c>
+      <c r="M66" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67" s="1">
+        <v>6</v>
+      </c>
+      <c r="C67" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" s="1">
+        <v>9</v>
+      </c>
+      <c r="E67" t="s">
+        <v>9</v>
+      </c>
+      <c r="F67" s="1">
+        <v>19</v>
+      </c>
+      <c r="G67" t="s">
+        <v>9</v>
+      </c>
+      <c r="H67" s="1">
+        <v>24</v>
+      </c>
+      <c r="I67" t="s">
+        <v>9</v>
+      </c>
+      <c r="J67" s="1">
+        <v>5</v>
+      </c>
+      <c r="K67" t="s">
+        <v>9</v>
+      </c>
+      <c r="L67" s="1">
+        <v>13</v>
+      </c>
+      <c r="M67" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68" s="1">
+        <v>6</v>
+      </c>
+      <c r="C68" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" s="1">
+        <v>9</v>
+      </c>
+      <c r="E68" t="s">
+        <v>9</v>
+      </c>
+      <c r="F68" s="1">
+        <v>19</v>
+      </c>
+      <c r="G68" t="s">
+        <v>9</v>
+      </c>
+      <c r="H68" s="1">
+        <v>24</v>
+      </c>
+      <c r="I68" t="s">
+        <v>9</v>
+      </c>
+      <c r="J68" s="1">
+        <v>17</v>
+      </c>
+      <c r="K68" t="s">
+        <v>9</v>
+      </c>
+      <c r="L68" s="1">
+        <v>18</v>
+      </c>
+      <c r="M68" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B69" s="1">
+        <v>5</v>
+      </c>
+      <c r="C69" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="1">
+        <v>14</v>
+      </c>
+      <c r="E69" t="s">
+        <v>9</v>
+      </c>
+      <c r="F69" s="1">
+        <v>15</v>
+      </c>
+      <c r="G69" t="s">
+        <v>9</v>
+      </c>
+      <c r="H69" s="1">
+        <v>16</v>
+      </c>
+      <c r="I69" t="s">
+        <v>9</v>
+      </c>
+      <c r="J69" s="1">
+        <v>7</v>
+      </c>
+      <c r="K69" t="s">
+        <v>9</v>
+      </c>
+      <c r="L69" s="1">
+        <v>8</v>
+      </c>
+      <c r="M69" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70" s="1">
+        <v>5</v>
+      </c>
+      <c r="C70" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" s="1">
+        <v>14</v>
+      </c>
+      <c r="E70" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" s="1">
+        <v>15</v>
+      </c>
+      <c r="G70" t="s">
+        <v>9</v>
+      </c>
+      <c r="H70" s="1">
+        <v>16</v>
+      </c>
+      <c r="I70" t="s">
+        <v>9</v>
+      </c>
+      <c r="J70" s="1">
+        <v>18</v>
+      </c>
+      <c r="K70" t="s">
+        <v>9</v>
+      </c>
+      <c r="L70" s="1">
+        <v>22</v>
+      </c>
+      <c r="M70" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71" s="1">
+        <v>5</v>
+      </c>
+      <c r="C71" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" s="1">
+        <v>14</v>
+      </c>
+      <c r="E71" t="s">
+        <v>9</v>
+      </c>
+      <c r="F71" s="1">
+        <v>15</v>
+      </c>
+      <c r="G71" t="s">
+        <v>9</v>
+      </c>
+      <c r="H71" s="1">
+        <v>16</v>
+      </c>
+      <c r="I71" t="s">
+        <v>9</v>
+      </c>
+      <c r="J71" s="1">
+        <v>13</v>
+      </c>
+      <c r="K71" t="s">
+        <v>9</v>
+      </c>
+      <c r="L71" s="1">
+        <v>20</v>
+      </c>
+      <c r="M71" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" s="1">
+        <v>5</v>
+      </c>
+      <c r="C72" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" s="1">
+        <v>14</v>
+      </c>
+      <c r="E72" t="s">
+        <v>9</v>
+      </c>
+      <c r="F72" s="1">
+        <v>15</v>
+      </c>
+      <c r="G72" t="s">
+        <v>9</v>
+      </c>
+      <c r="H72" s="1">
+        <v>16</v>
+      </c>
+      <c r="I72" t="s">
+        <v>9</v>
+      </c>
+      <c r="J72" s="1">
+        <v>4</v>
+      </c>
+      <c r="K72" t="s">
+        <v>9</v>
+      </c>
+      <c r="L72" s="1">
+        <v>23</v>
+      </c>
+      <c r="M72" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" s="1">
+        <v>5</v>
+      </c>
+      <c r="C73" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" s="1">
+        <v>14</v>
+      </c>
+      <c r="E73" t="s">
+        <v>9</v>
+      </c>
+      <c r="F73" s="1">
+        <v>15</v>
+      </c>
+      <c r="G73" t="s">
+        <v>9</v>
+      </c>
+      <c r="H73" s="1">
+        <v>16</v>
+      </c>
+      <c r="I73" t="s">
+        <v>9</v>
+      </c>
+      <c r="J73" s="1">
+        <v>12</v>
+      </c>
+      <c r="K73" t="s">
+        <v>9</v>
+      </c>
+      <c r="L73" s="1">
+        <v>25</v>
+      </c>
+      <c r="M73" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" s="1">
+        <v>5</v>
+      </c>
+      <c r="C74" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" s="1">
+        <v>14</v>
+      </c>
+      <c r="E74" t="s">
+        <v>9</v>
+      </c>
+      <c r="F74" s="1">
+        <v>15</v>
+      </c>
+      <c r="G74" t="s">
+        <v>9</v>
+      </c>
+      <c r="H74" s="1">
+        <v>16</v>
+      </c>
+      <c r="I74" t="s">
+        <v>9</v>
+      </c>
+      <c r="J74" s="1">
+        <v>9</v>
+      </c>
+      <c r="K74" t="s">
+        <v>9</v>
+      </c>
+      <c r="L74" s="1">
+        <v>10</v>
+      </c>
+      <c r="M74" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" s="1">
+        <v>5</v>
+      </c>
+      <c r="C75" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" s="1">
+        <v>14</v>
+      </c>
+      <c r="E75" t="s">
+        <v>9</v>
+      </c>
+      <c r="F75" s="1">
+        <v>15</v>
+      </c>
+      <c r="G75" t="s">
+        <v>9</v>
+      </c>
+      <c r="H75" s="1">
+        <v>16</v>
+      </c>
+      <c r="I75" t="s">
+        <v>9</v>
+      </c>
+      <c r="J75" s="1">
+        <v>11</v>
+      </c>
+      <c r="K75" t="s">
+        <v>9</v>
+      </c>
+      <c r="L75" s="1">
+        <v>20</v>
+      </c>
+      <c r="M75" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B76" s="1">
+        <v>5</v>
+      </c>
+      <c r="C76" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76" s="1">
+        <v>14</v>
+      </c>
+      <c r="E76" t="s">
+        <v>9</v>
+      </c>
+      <c r="F76" s="1">
+        <v>15</v>
+      </c>
+      <c r="G76" t="s">
+        <v>9</v>
+      </c>
+      <c r="H76" s="1">
+        <v>16</v>
+      </c>
+      <c r="I76" t="s">
+        <v>9</v>
+      </c>
+      <c r="J76" s="1">
+        <v>2</v>
+      </c>
+      <c r="K76" t="s">
+        <v>9</v>
+      </c>
+      <c r="L76" s="1">
+        <v>21</v>
+      </c>
+      <c r="M76" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B77" s="1">
+        <v>5</v>
+      </c>
+      <c r="C77" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77" s="1">
+        <v>14</v>
+      </c>
+      <c r="E77" t="s">
+        <v>9</v>
+      </c>
+      <c r="F77" s="1">
+        <v>15</v>
+      </c>
+      <c r="G77" t="s">
+        <v>9</v>
+      </c>
+      <c r="H77" s="1">
+        <v>16</v>
+      </c>
+      <c r="I77" t="s">
+        <v>9</v>
+      </c>
+      <c r="J77" s="1">
+        <v>17</v>
+      </c>
+      <c r="K77" t="s">
+        <v>9</v>
+      </c>
+      <c r="L77" s="1">
+        <v>18</v>
+      </c>
+      <c r="M77" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B78" s="1">
+        <v>5</v>
+      </c>
+      <c r="C78" t="s">
+        <v>9</v>
+      </c>
+      <c r="D78" s="1">
+        <v>14</v>
+      </c>
+      <c r="E78" t="s">
+        <v>9</v>
+      </c>
+      <c r="F78" s="1">
+        <v>15</v>
+      </c>
+      <c r="G78" t="s">
+        <v>9</v>
+      </c>
+      <c r="H78" s="1">
+        <v>16</v>
+      </c>
+      <c r="I78" t="s">
+        <v>9</v>
+      </c>
+      <c r="J78" s="1">
+        <v>12</v>
+      </c>
+      <c r="K78" t="s">
+        <v>9</v>
+      </c>
+      <c r="L78" s="1">
+        <v>24</v>
+      </c>
+      <c r="M78" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B79" s="1">
+        <v>4</v>
+      </c>
+      <c r="C79" t="s">
+        <v>9</v>
+      </c>
+      <c r="D79" s="1">
+        <v>8</v>
+      </c>
+      <c r="E79" t="s">
+        <v>9</v>
+      </c>
+      <c r="F79" s="1">
+        <v>13</v>
+      </c>
+      <c r="G79" t="s">
+        <v>9</v>
+      </c>
+      <c r="H79" s="1">
+        <v>16</v>
+      </c>
+      <c r="I79" t="s">
+        <v>9</v>
+      </c>
+      <c r="J79" s="1">
+        <v>3</v>
+      </c>
+      <c r="K79" t="s">
+        <v>9</v>
+      </c>
+      <c r="L79" s="1">
+        <v>14</v>
+      </c>
+      <c r="M79" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B80" s="1">
+        <v>4</v>
+      </c>
+      <c r="C80" t="s">
+        <v>9</v>
+      </c>
+      <c r="D80" s="1">
+        <v>8</v>
+      </c>
+      <c r="E80" t="s">
+        <v>9</v>
+      </c>
+      <c r="F80" s="1">
+        <v>13</v>
+      </c>
+      <c r="G80" t="s">
+        <v>9</v>
+      </c>
+      <c r="H80" s="1">
+        <v>16</v>
+      </c>
+      <c r="I80" t="s">
+        <v>9</v>
+      </c>
+      <c r="J80" s="1">
+        <v>18</v>
+      </c>
+      <c r="K80" t="s">
+        <v>9</v>
+      </c>
+      <c r="L80" s="1">
+        <v>22</v>
+      </c>
+      <c r="M80" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B81" s="1">
+        <v>4</v>
+      </c>
+      <c r="C81" t="s">
+        <v>9</v>
+      </c>
+      <c r="D81" s="1">
+        <v>8</v>
+      </c>
+      <c r="E81" t="s">
+        <v>9</v>
+      </c>
+      <c r="F81" s="1">
+        <v>13</v>
+      </c>
+      <c r="G81" t="s">
+        <v>9</v>
+      </c>
+      <c r="H81" s="1">
+        <v>16</v>
+      </c>
+      <c r="I81" t="s">
+        <v>9</v>
+      </c>
+      <c r="J81" s="1">
+        <v>6</v>
+      </c>
+      <c r="K81" t="s">
+        <v>9</v>
+      </c>
+      <c r="L81" s="1">
+        <v>24</v>
+      </c>
+      <c r="M81" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B82" s="1">
+        <v>4</v>
+      </c>
+      <c r="C82" t="s">
+        <v>9</v>
+      </c>
+      <c r="D82" s="1">
+        <v>8</v>
+      </c>
+      <c r="E82" t="s">
+        <v>9</v>
+      </c>
+      <c r="F82" s="1">
+        <v>13</v>
+      </c>
+      <c r="G82" t="s">
+        <v>9</v>
+      </c>
+      <c r="H82" s="1">
+        <v>16</v>
+      </c>
+      <c r="I82" t="s">
+        <v>9</v>
+      </c>
+      <c r="J82" s="1">
+        <v>15</v>
+      </c>
+      <c r="K82" t="s">
+        <v>9</v>
+      </c>
+      <c r="L82" s="1">
+        <v>19</v>
+      </c>
+      <c r="M82" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B83" s="1">
+        <v>4</v>
+      </c>
+      <c r="C83" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83" s="1">
+        <v>8</v>
+      </c>
+      <c r="E83" t="s">
+        <v>9</v>
+      </c>
+      <c r="F83" s="1">
+        <v>13</v>
+      </c>
+      <c r="G83" t="s">
+        <v>9</v>
+      </c>
+      <c r="H83" s="1">
+        <v>16</v>
+      </c>
+      <c r="I83" t="s">
+        <v>9</v>
+      </c>
+      <c r="J83" s="1">
+        <v>12</v>
+      </c>
+      <c r="K83" t="s">
+        <v>9</v>
+      </c>
+      <c r="L83" s="1">
+        <v>25</v>
+      </c>
+      <c r="M83" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B84" s="1">
+        <v>4</v>
+      </c>
+      <c r="C84" t="s">
+        <v>9</v>
+      </c>
+      <c r="D84" s="1">
+        <v>8</v>
+      </c>
+      <c r="E84" t="s">
+        <v>9</v>
+      </c>
+      <c r="F84" s="1">
+        <v>13</v>
+      </c>
+      <c r="G84" t="s">
+        <v>9</v>
+      </c>
+      <c r="H84" s="1">
+        <v>16</v>
+      </c>
+      <c r="I84" t="s">
+        <v>9</v>
+      </c>
+      <c r="J84" s="1">
+        <v>9</v>
+      </c>
+      <c r="K84" t="s">
+        <v>9</v>
+      </c>
+      <c r="L84" s="1">
+        <v>10</v>
+      </c>
+      <c r="M84" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B85" s="1">
+        <v>4</v>
+      </c>
+      <c r="C85" t="s">
+        <v>9</v>
+      </c>
+      <c r="D85" s="1">
+        <v>8</v>
+      </c>
+      <c r="E85" t="s">
+        <v>9</v>
+      </c>
+      <c r="F85" s="1">
+        <v>13</v>
+      </c>
+      <c r="G85" t="s">
+        <v>9</v>
+      </c>
+      <c r="H85" s="1">
+        <v>16</v>
+      </c>
+      <c r="I85" t="s">
+        <v>9</v>
+      </c>
+      <c r="J85" s="1">
+        <v>11</v>
+      </c>
+      <c r="K85" t="s">
+        <v>9</v>
+      </c>
+      <c r="L85" s="1">
+        <v>20</v>
+      </c>
+      <c r="M85" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B86" s="1">
+        <v>4</v>
+      </c>
+      <c r="C86" t="s">
+        <v>9</v>
+      </c>
+      <c r="D86" s="1">
+        <v>8</v>
+      </c>
+      <c r="E86" t="s">
+        <v>9</v>
+      </c>
+      <c r="F86" s="1">
+        <v>13</v>
+      </c>
+      <c r="G86" t="s">
+        <v>9</v>
+      </c>
+      <c r="H86" s="1">
+        <v>16</v>
+      </c>
+      <c r="I86" t="s">
+        <v>9</v>
+      </c>
+      <c r="J86" s="1">
+        <v>2</v>
+      </c>
+      <c r="K86" t="s">
+        <v>9</v>
+      </c>
+      <c r="L86" s="1">
+        <v>21</v>
+      </c>
+      <c r="M86" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B87" s="1">
+        <v>4</v>
+      </c>
+      <c r="C87" t="s">
+        <v>9</v>
+      </c>
+      <c r="D87" s="1">
+        <v>8</v>
+      </c>
+      <c r="E87" t="s">
+        <v>9</v>
+      </c>
+      <c r="F87" s="1">
+        <v>13</v>
+      </c>
+      <c r="G87" t="s">
+        <v>9</v>
+      </c>
+      <c r="H87" s="1">
+        <v>16</v>
+      </c>
+      <c r="I87" t="s">
+        <v>9</v>
+      </c>
+      <c r="J87" s="1">
+        <v>17</v>
+      </c>
+      <c r="K87" t="s">
+        <v>9</v>
+      </c>
+      <c r="L87" s="1">
+        <v>18</v>
+      </c>
+      <c r="M87" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B88" s="1">
+        <v>4</v>
+      </c>
+      <c r="C88" t="s">
+        <v>9</v>
+      </c>
+      <c r="D88" s="1">
+        <v>5</v>
+      </c>
+      <c r="E88" t="s">
+        <v>9</v>
+      </c>
+      <c r="F88" s="1">
+        <v>10</v>
+      </c>
+      <c r="G88" t="s">
+        <v>9</v>
+      </c>
+      <c r="H88" s="1">
+        <v>12</v>
+      </c>
+      <c r="I88" t="s">
+        <v>9</v>
+      </c>
+      <c r="J88" s="1">
+        <v>7</v>
+      </c>
+      <c r="K88" t="s">
+        <v>9</v>
+      </c>
+      <c r="L88" s="1">
+        <v>8</v>
+      </c>
+      <c r="M88" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B89" s="1">
+        <v>4</v>
+      </c>
+      <c r="C89" t="s">
+        <v>9</v>
+      </c>
+      <c r="D89" s="1">
+        <v>5</v>
+      </c>
+      <c r="E89" t="s">
+        <v>9</v>
+      </c>
+      <c r="F89" s="1">
+        <v>10</v>
+      </c>
+      <c r="G89" t="s">
+        <v>9</v>
+      </c>
+      <c r="H89" s="1">
+        <v>12</v>
+      </c>
+      <c r="I89" t="s">
+        <v>9</v>
+      </c>
+      <c r="J89" s="1">
+        <v>3</v>
+      </c>
+      <c r="K89" t="s">
+        <v>9</v>
+      </c>
+      <c r="L89" s="1">
+        <v>14</v>
+      </c>
+      <c r="M89" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B90" s="1">
+        <v>4</v>
+      </c>
+      <c r="C90" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90" s="1">
+        <v>5</v>
+      </c>
+      <c r="E90" t="s">
+        <v>9</v>
+      </c>
+      <c r="F90" s="1">
+        <v>10</v>
+      </c>
+      <c r="G90" t="s">
+        <v>9</v>
+      </c>
+      <c r="H90" s="1">
+        <v>12</v>
+      </c>
+      <c r="I90" t="s">
+        <v>9</v>
+      </c>
+      <c r="J90" s="1">
+        <v>18</v>
+      </c>
+      <c r="K90" t="s">
+        <v>9</v>
+      </c>
+      <c r="L90" s="1">
+        <v>22</v>
+      </c>
+      <c r="M90" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B91" s="1">
+        <v>4</v>
+      </c>
+      <c r="C91" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91" s="1">
+        <v>5</v>
+      </c>
+      <c r="E91" t="s">
+        <v>9</v>
+      </c>
+      <c r="F91" s="1">
+        <v>10</v>
+      </c>
+      <c r="G91" t="s">
+        <v>9</v>
+      </c>
+      <c r="H91" s="1">
+        <v>12</v>
+      </c>
+      <c r="I91" t="s">
+        <v>9</v>
+      </c>
+      <c r="J91" s="1">
+        <v>16</v>
+      </c>
+      <c r="K91" t="s">
+        <v>9</v>
+      </c>
+      <c r="L91" s="1">
+        <v>24</v>
+      </c>
+      <c r="M91" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B92" s="1">
+        <v>4</v>
+      </c>
+      <c r="C92" t="s">
+        <v>9</v>
+      </c>
+      <c r="D92" s="1">
+        <v>5</v>
+      </c>
+      <c r="E92" t="s">
+        <v>9</v>
+      </c>
+      <c r="F92" s="1">
+        <v>10</v>
+      </c>
+      <c r="G92" t="s">
+        <v>9</v>
+      </c>
+      <c r="H92" s="1">
+        <v>12</v>
+      </c>
+      <c r="I92" t="s">
+        <v>9</v>
+      </c>
+      <c r="J92" s="1">
+        <v>13</v>
+      </c>
+      <c r="K92" t="s">
+        <v>9</v>
+      </c>
+      <c r="L92" s="1">
+        <v>20</v>
+      </c>
+      <c r="M92" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B93" s="1">
+        <v>4</v>
+      </c>
+      <c r="C93" t="s">
+        <v>9</v>
+      </c>
+      <c r="D93" s="1">
+        <v>5</v>
+      </c>
+      <c r="E93" t="s">
+        <v>9</v>
+      </c>
+      <c r="F93" s="1">
+        <v>10</v>
+      </c>
+      <c r="G93" t="s">
+        <v>9</v>
+      </c>
+      <c r="H93" s="1">
+        <v>12</v>
+      </c>
+      <c r="I93" t="s">
+        <v>9</v>
+      </c>
+      <c r="J93" s="1">
+        <v>15</v>
+      </c>
+      <c r="K93" t="s">
+        <v>9</v>
+      </c>
+      <c r="L93" s="1">
+        <v>19</v>
+      </c>
+      <c r="M93" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B94" s="1">
+        <v>4</v>
+      </c>
+      <c r="C94" t="s">
+        <v>9</v>
+      </c>
+      <c r="D94" s="1">
+        <v>5</v>
+      </c>
+      <c r="E94" t="s">
+        <v>9</v>
+      </c>
+      <c r="F94" s="1">
+        <v>10</v>
+      </c>
+      <c r="G94" t="s">
+        <v>9</v>
+      </c>
+      <c r="H94" s="1">
+        <v>12</v>
+      </c>
+      <c r="I94" t="s">
+        <v>9</v>
+      </c>
+      <c r="J94" s="1">
+        <v>11</v>
+      </c>
+      <c r="K94" t="s">
+        <v>9</v>
+      </c>
+      <c r="L94" s="1">
+        <v>20</v>
+      </c>
+      <c r="M94" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B95" s="1">
+        <v>4</v>
+      </c>
+      <c r="C95" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" s="1">
+        <v>5</v>
+      </c>
+      <c r="E95" t="s">
+        <v>9</v>
+      </c>
+      <c r="F95" s="1">
+        <v>10</v>
+      </c>
+      <c r="G95" t="s">
+        <v>9</v>
+      </c>
+      <c r="H95" s="1">
+        <v>12</v>
+      </c>
+      <c r="I95" t="s">
+        <v>9</v>
+      </c>
+      <c r="J95" s="1">
+        <v>2</v>
+      </c>
+      <c r="K95" t="s">
+        <v>9</v>
+      </c>
+      <c r="L95" s="1">
+        <v>21</v>
+      </c>
+      <c r="M95" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B96" s="1">
+        <v>4</v>
+      </c>
+      <c r="C96" t="s">
+        <v>9</v>
+      </c>
+      <c r="D96" s="1">
+        <v>5</v>
+      </c>
+      <c r="E96" t="s">
+        <v>9</v>
+      </c>
+      <c r="F96" s="1">
+        <v>10</v>
+      </c>
+      <c r="G96" t="s">
+        <v>9</v>
+      </c>
+      <c r="H96" s="1">
+        <v>12</v>
+      </c>
+      <c r="I96" t="s">
+        <v>9</v>
+      </c>
+      <c r="J96" s="1">
+        <v>17</v>
+      </c>
+      <c r="K96" t="s">
+        <v>9</v>
+      </c>
+      <c r="L96" s="1">
+        <v>18</v>
+      </c>
+      <c r="M96" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B97" s="1">
+        <v>3</v>
+      </c>
+      <c r="C97" t="s">
+        <v>9</v>
+      </c>
+      <c r="D97" s="1">
+        <v>18</v>
+      </c>
+      <c r="E97" t="s">
+        <v>9</v>
+      </c>
+      <c r="F97" s="1">
+        <v>22</v>
+      </c>
+      <c r="G97" t="s">
+        <v>9</v>
+      </c>
+      <c r="H97" s="1">
+        <v>23</v>
+      </c>
+      <c r="I97" t="s">
+        <v>9</v>
+      </c>
+      <c r="J97" s="1">
+        <v>7</v>
+      </c>
+      <c r="K97" t="s">
+        <v>9</v>
+      </c>
+      <c r="L97" s="1">
+        <v>8</v>
+      </c>
+      <c r="M97" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B98" s="1">
+        <v>3</v>
+      </c>
+      <c r="C98" t="s">
+        <v>9</v>
+      </c>
+      <c r="D98" s="1">
+        <v>18</v>
+      </c>
+      <c r="E98" t="s">
+        <v>9</v>
+      </c>
+      <c r="F98" s="1">
+        <v>22</v>
+      </c>
+      <c r="G98" t="s">
+        <v>9</v>
+      </c>
+      <c r="H98" s="1">
+        <v>23</v>
+      </c>
+      <c r="I98" t="s">
+        <v>9</v>
+      </c>
+      <c r="J98" s="1">
+        <v>16</v>
+      </c>
+      <c r="K98" t="s">
+        <v>9</v>
+      </c>
+      <c r="L98" s="1">
+        <v>24</v>
+      </c>
+      <c r="M98" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B99" s="1">
+        <v>3</v>
+      </c>
+      <c r="C99" t="s">
+        <v>9</v>
+      </c>
+      <c r="D99" s="1">
+        <v>18</v>
+      </c>
+      <c r="E99" t="s">
+        <v>9</v>
+      </c>
+      <c r="F99" s="1">
+        <v>22</v>
+      </c>
+      <c r="G99" t="s">
+        <v>9</v>
+      </c>
+      <c r="H99" s="1">
+        <v>23</v>
+      </c>
+      <c r="I99" t="s">
+        <v>9</v>
+      </c>
+      <c r="J99" s="1">
+        <v>13</v>
+      </c>
+      <c r="K99" t="s">
+        <v>9</v>
+      </c>
+      <c r="L99" s="1">
+        <v>20</v>
+      </c>
+      <c r="M99" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B100" s="1">
+        <v>3</v>
+      </c>
+      <c r="C100" t="s">
+        <v>9</v>
+      </c>
+      <c r="D100" s="1">
+        <v>18</v>
+      </c>
+      <c r="E100" t="s">
+        <v>9</v>
+      </c>
+      <c r="F100" s="1">
+        <v>22</v>
+      </c>
+      <c r="G100" t="s">
+        <v>9</v>
+      </c>
+      <c r="H100" s="1">
+        <v>23</v>
+      </c>
+      <c r="I100" t="s">
+        <v>9</v>
+      </c>
+      <c r="J100" s="1">
+        <v>15</v>
+      </c>
+      <c r="K100" t="s">
+        <v>9</v>
+      </c>
+      <c r="L100" s="1">
+        <v>19</v>
+      </c>
+      <c r="M100" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B101" s="1">
+        <v>3</v>
+      </c>
+      <c r="C101" t="s">
+        <v>9</v>
+      </c>
+      <c r="D101" s="1">
+        <v>18</v>
+      </c>
+      <c r="E101" t="s">
+        <v>9</v>
+      </c>
+      <c r="F101" s="1">
+        <v>22</v>
+      </c>
+      <c r="G101" t="s">
+        <v>9</v>
+      </c>
+      <c r="H101" s="1">
+        <v>23</v>
+      </c>
+      <c r="I101" t="s">
+        <v>9</v>
+      </c>
+      <c r="J101" s="1">
+        <v>12</v>
+      </c>
+      <c r="K101" t="s">
+        <v>9</v>
+      </c>
+      <c r="L101" s="1">
+        <v>25</v>
+      </c>
+      <c r="M101" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B102" s="1">
+        <v>3</v>
+      </c>
+      <c r="C102" t="s">
+        <v>9</v>
+      </c>
+      <c r="D102" s="1">
+        <v>18</v>
+      </c>
+      <c r="E102" t="s">
+        <v>9</v>
+      </c>
+      <c r="F102" s="1">
+        <v>22</v>
+      </c>
+      <c r="G102" t="s">
+        <v>9</v>
+      </c>
+      <c r="H102" s="1">
+        <v>23</v>
+      </c>
+      <c r="I102" t="s">
+        <v>9</v>
+      </c>
+      <c r="J102" s="1">
+        <v>9</v>
+      </c>
+      <c r="K102" t="s">
+        <v>9</v>
+      </c>
+      <c r="L102" s="1">
+        <v>10</v>
+      </c>
+      <c r="M102" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B103" s="1">
+        <v>3</v>
+      </c>
+      <c r="C103" t="s">
+        <v>9</v>
+      </c>
+      <c r="D103" s="1">
+        <v>18</v>
+      </c>
+      <c r="E103" t="s">
+        <v>9</v>
+      </c>
+      <c r="F103" s="1">
+        <v>22</v>
+      </c>
+      <c r="G103" t="s">
+        <v>9</v>
+      </c>
+      <c r="H103" s="1">
+        <v>23</v>
+      </c>
+      <c r="I103" t="s">
+        <v>9</v>
+      </c>
+      <c r="J103" s="1">
+        <v>11</v>
+      </c>
+      <c r="K103" t="s">
+        <v>9</v>
+      </c>
+      <c r="L103" s="1">
+        <v>20</v>
+      </c>
+      <c r="M103" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B104" s="1">
+        <v>3</v>
+      </c>
+      <c r="C104" t="s">
+        <v>9</v>
+      </c>
+      <c r="D104" s="1">
+        <v>18</v>
+      </c>
+      <c r="E104" t="s">
+        <v>9</v>
+      </c>
+      <c r="F104" s="1">
+        <v>22</v>
+      </c>
+      <c r="G104" t="s">
+        <v>9</v>
+      </c>
+      <c r="H104" s="1">
+        <v>23</v>
+      </c>
+      <c r="I104" t="s">
+        <v>9</v>
+      </c>
+      <c r="J104" s="1">
+        <v>2</v>
+      </c>
+      <c r="K104" t="s">
+        <v>9</v>
+      </c>
+      <c r="L104" s="1">
+        <v>21</v>
+      </c>
+      <c r="M104" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B105" s="1">
+        <v>3</v>
+      </c>
+      <c r="C105" t="s">
+        <v>9</v>
+      </c>
+      <c r="D105" s="1">
+        <v>18</v>
+      </c>
+      <c r="E105" t="s">
+        <v>9</v>
+      </c>
+      <c r="F105" s="1">
+        <v>22</v>
+      </c>
+      <c r="G105" t="s">
+        <v>9</v>
+      </c>
+      <c r="H105" s="1">
+        <v>23</v>
+      </c>
+      <c r="I105" t="s">
+        <v>9</v>
+      </c>
+      <c r="J105" s="1">
+        <v>5</v>
+      </c>
+      <c r="K105" t="s">
+        <v>9</v>
+      </c>
+      <c r="L105" s="1">
+        <v>13</v>
+      </c>
+      <c r="M105" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B106" s="1">
+        <v>3</v>
+      </c>
+      <c r="C106" t="s">
+        <v>9</v>
+      </c>
+      <c r="D106" s="1">
+        <v>18</v>
+      </c>
+      <c r="E106" t="s">
+        <v>9</v>
+      </c>
+      <c r="F106" s="1">
+        <v>22</v>
+      </c>
+      <c r="G106" t="s">
+        <v>9</v>
+      </c>
+      <c r="H106" s="1">
+        <v>23</v>
+      </c>
+      <c r="I106" t="s">
+        <v>9</v>
+      </c>
+      <c r="J106" s="1">
+        <v>12</v>
+      </c>
+      <c r="K106" t="s">
+        <v>9</v>
+      </c>
+      <c r="L106" s="1">
+        <v>24</v>
+      </c>
+      <c r="M106" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B107" s="1">
+        <v>3</v>
+      </c>
+      <c r="C107" t="s">
+        <v>9</v>
+      </c>
+      <c r="D107" s="1">
+        <v>17</v>
+      </c>
+      <c r="E107" t="s">
+        <v>9</v>
+      </c>
+      <c r="F107" s="1">
+        <v>20</v>
+      </c>
+      <c r="G107" t="s">
+        <v>9</v>
+      </c>
+      <c r="H107" s="1">
+        <v>23</v>
+      </c>
+      <c r="I107" t="s">
+        <v>9</v>
+      </c>
+      <c r="J107" s="1">
+        <v>7</v>
+      </c>
+      <c r="K107" t="s">
+        <v>9</v>
+      </c>
+      <c r="L107" s="1">
+        <v>8</v>
+      </c>
+      <c r="M107" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B108" s="1">
+        <v>3</v>
+      </c>
+      <c r="C108" t="s">
+        <v>9</v>
+      </c>
+      <c r="D108" s="1">
+        <v>17</v>
+      </c>
+      <c r="E108" t="s">
+        <v>9</v>
+      </c>
+      <c r="F108" s="1">
+        <v>20</v>
+      </c>
+      <c r="G108" t="s">
+        <v>9</v>
+      </c>
+      <c r="H108" s="1">
+        <v>23</v>
+      </c>
+      <c r="I108" t="s">
+        <v>9</v>
+      </c>
+      <c r="J108" s="1">
+        <v>18</v>
+      </c>
+      <c r="K108" t="s">
+        <v>9</v>
+      </c>
+      <c r="L108" s="1">
+        <v>22</v>
+      </c>
+      <c r="M108" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B109" s="1">
+        <v>3</v>
+      </c>
+      <c r="C109" t="s">
+        <v>9</v>
+      </c>
+      <c r="D109" s="1">
+        <v>17</v>
+      </c>
+      <c r="E109" t="s">
+        <v>9</v>
+      </c>
+      <c r="F109" s="1">
+        <v>20</v>
+      </c>
+      <c r="G109" t="s">
+        <v>9</v>
+      </c>
+      <c r="H109" s="1">
+        <v>23</v>
+      </c>
+      <c r="I109" t="s">
+        <v>9</v>
+      </c>
+      <c r="J109" s="1">
+        <v>16</v>
+      </c>
+      <c r="K109" t="s">
+        <v>9</v>
+      </c>
+      <c r="L109" s="1">
+        <v>24</v>
+      </c>
+      <c r="M109" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B110" s="1">
+        <v>3</v>
+      </c>
+      <c r="C110" t="s">
+        <v>9</v>
+      </c>
+      <c r="D110" s="1">
+        <v>17</v>
+      </c>
+      <c r="E110" t="s">
+        <v>9</v>
+      </c>
+      <c r="F110" s="1">
+        <v>20</v>
+      </c>
+      <c r="G110" t="s">
+        <v>9</v>
+      </c>
+      <c r="H110" s="1">
+        <v>23</v>
+      </c>
+      <c r="I110" t="s">
+        <v>9</v>
+      </c>
+      <c r="J110" s="1">
+        <v>15</v>
+      </c>
+      <c r="K110" t="s">
+        <v>9</v>
+      </c>
+      <c r="L110" s="1">
+        <v>19</v>
+      </c>
+      <c r="M110" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B111" s="1">
+        <v>3</v>
+      </c>
+      <c r="C111" t="s">
+        <v>9</v>
+      </c>
+      <c r="D111" s="1">
+        <v>17</v>
+      </c>
+      <c r="E111" t="s">
+        <v>9</v>
+      </c>
+      <c r="F111" s="1">
+        <v>20</v>
+      </c>
+      <c r="G111" t="s">
+        <v>9</v>
+      </c>
+      <c r="H111" s="1">
+        <v>23</v>
+      </c>
+      <c r="I111" t="s">
+        <v>9</v>
+      </c>
+      <c r="J111" s="1">
+        <v>12</v>
+      </c>
+      <c r="K111" t="s">
+        <v>9</v>
+      </c>
+      <c r="L111" s="1">
+        <v>25</v>
+      </c>
+      <c r="M111" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B112" s="1">
+        <v>3</v>
+      </c>
+      <c r="C112" t="s">
+        <v>9</v>
+      </c>
+      <c r="D112" s="1">
+        <v>17</v>
+      </c>
+      <c r="E112" t="s">
+        <v>9</v>
+      </c>
+      <c r="F112" s="1">
+        <v>20</v>
+      </c>
+      <c r="G112" t="s">
+        <v>9</v>
+      </c>
+      <c r="H112" s="1">
+        <v>23</v>
+      </c>
+      <c r="I112" t="s">
+        <v>9</v>
+      </c>
+      <c r="J112" s="1">
+        <v>9</v>
+      </c>
+      <c r="K112" t="s">
+        <v>9</v>
+      </c>
+      <c r="L112" s="1">
+        <v>10</v>
+      </c>
+      <c r="M112" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B113" s="1">
+        <v>3</v>
+      </c>
+      <c r="C113" t="s">
+        <v>9</v>
+      </c>
+      <c r="D113" s="1">
+        <v>17</v>
+      </c>
+      <c r="E113" t="s">
+        <v>9</v>
+      </c>
+      <c r="F113" s="1">
+        <v>20</v>
+      </c>
+      <c r="G113" t="s">
+        <v>9</v>
+      </c>
+      <c r="H113" s="1">
+        <v>23</v>
+      </c>
+      <c r="I113" t="s">
+        <v>9</v>
+      </c>
+      <c r="J113" s="1">
+        <v>2</v>
+      </c>
+      <c r="K113" t="s">
+        <v>9</v>
+      </c>
+      <c r="L113" s="1">
+        <v>21</v>
+      </c>
+      <c r="M113" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B114" s="1">
+        <v>3</v>
+      </c>
+      <c r="C114" t="s">
+        <v>9</v>
+      </c>
+      <c r="D114" s="1">
+        <v>17</v>
+      </c>
+      <c r="E114" t="s">
+        <v>9</v>
+      </c>
+      <c r="F114" s="1">
+        <v>20</v>
+      </c>
+      <c r="G114" t="s">
+        <v>9</v>
+      </c>
+      <c r="H114" s="1">
+        <v>23</v>
+      </c>
+      <c r="I114" t="s">
+        <v>9</v>
+      </c>
+      <c r="J114" s="1">
+        <v>5</v>
+      </c>
+      <c r="K114" t="s">
+        <v>9</v>
+      </c>
+      <c r="L114" s="1">
+        <v>13</v>
+      </c>
+      <c r="M114" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B115" s="1">
+        <v>3</v>
+      </c>
+      <c r="C115" t="s">
+        <v>9</v>
+      </c>
+      <c r="D115" s="1">
+        <v>17</v>
+      </c>
+      <c r="E115" t="s">
+        <v>9</v>
+      </c>
+      <c r="F115" s="1">
+        <v>20</v>
+      </c>
+      <c r="G115" t="s">
+        <v>9</v>
+      </c>
+      <c r="H115" s="1">
+        <v>23</v>
+      </c>
+      <c r="I115" t="s">
+        <v>9</v>
+      </c>
+      <c r="J115" s="1">
+        <v>12</v>
+      </c>
+      <c r="K115" t="s">
+        <v>9</v>
+      </c>
+      <c r="L115" s="1">
+        <v>24</v>
+      </c>
+      <c r="M115" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B116" s="1">
+        <v>3</v>
+      </c>
+      <c r="C116" t="s">
+        <v>9</v>
+      </c>
+      <c r="D116" s="1">
+        <v>11</v>
+      </c>
+      <c r="E116" t="s">
+        <v>9</v>
+      </c>
+      <c r="F116" s="1">
+        <v>18</v>
+      </c>
+      <c r="G116" t="s">
+        <v>9</v>
+      </c>
+      <c r="H116" s="1">
+        <v>23</v>
+      </c>
+      <c r="I116" t="s">
+        <v>9</v>
+      </c>
+      <c r="J116" s="1">
+        <v>7</v>
+      </c>
+      <c r="K116" t="s">
+        <v>9</v>
+      </c>
+      <c r="L116" s="1">
+        <v>8</v>
+      </c>
+      <c r="M116" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B117" s="1">
+        <v>3</v>
+      </c>
+      <c r="C117" t="s">
+        <v>9</v>
+      </c>
+      <c r="D117" s="1">
+        <v>11</v>
+      </c>
+      <c r="E117" t="s">
+        <v>9</v>
+      </c>
+      <c r="F117" s="1">
+        <v>18</v>
+      </c>
+      <c r="G117" t="s">
+        <v>9</v>
+      </c>
+      <c r="H117" s="1">
+        <v>23</v>
+      </c>
+      <c r="I117" t="s">
+        <v>9</v>
+      </c>
+      <c r="J117" s="1">
+        <v>16</v>
+      </c>
+      <c r="K117" t="s">
+        <v>9</v>
+      </c>
+      <c r="L117" s="1">
+        <v>24</v>
+      </c>
+      <c r="M117" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B118" s="1">
+        <v>3</v>
+      </c>
+      <c r="C118" t="s">
+        <v>9</v>
+      </c>
+      <c r="D118" s="1">
+        <v>11</v>
+      </c>
+      <c r="E118" t="s">
+        <v>9</v>
+      </c>
+      <c r="F118" s="1">
+        <v>18</v>
+      </c>
+      <c r="G118" t="s">
+        <v>9</v>
+      </c>
+      <c r="H118" s="1">
+        <v>23</v>
+      </c>
+      <c r="I118" t="s">
+        <v>9</v>
+      </c>
+      <c r="J118" s="1">
+        <v>13</v>
+      </c>
+      <c r="K118" t="s">
+        <v>9</v>
+      </c>
+      <c r="L118" s="1">
+        <v>20</v>
+      </c>
+      <c r="M118" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B119" s="1">
+        <v>3</v>
+      </c>
+      <c r="C119" t="s">
+        <v>9</v>
+      </c>
+      <c r="D119" s="1">
+        <v>11</v>
+      </c>
+      <c r="E119" t="s">
+        <v>9</v>
+      </c>
+      <c r="F119" s="1">
+        <v>18</v>
+      </c>
+      <c r="G119" t="s">
+        <v>9</v>
+      </c>
+      <c r="H119" s="1">
+        <v>23</v>
+      </c>
+      <c r="I119" t="s">
+        <v>9</v>
+      </c>
+      <c r="J119" s="1">
+        <v>15</v>
+      </c>
+      <c r="K119" t="s">
+        <v>9</v>
+      </c>
+      <c r="L119" s="1">
+        <v>19</v>
+      </c>
+      <c r="M119" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B120" s="1">
+        <v>3</v>
+      </c>
+      <c r="C120" t="s">
+        <v>9</v>
+      </c>
+      <c r="D120" s="1">
+        <v>11</v>
+      </c>
+      <c r="E120" t="s">
+        <v>9</v>
+      </c>
+      <c r="F120" s="1">
+        <v>18</v>
+      </c>
+      <c r="G120" t="s">
+        <v>9</v>
+      </c>
+      <c r="H120" s="1">
+        <v>23</v>
+      </c>
+      <c r="I120" t="s">
+        <v>9</v>
+      </c>
+      <c r="J120" s="1">
+        <v>12</v>
+      </c>
+      <c r="K120" t="s">
+        <v>9</v>
+      </c>
+      <c r="L120" s="1">
+        <v>25</v>
+      </c>
+      <c r="M120" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B121" s="1">
+        <v>3</v>
+      </c>
+      <c r="C121" t="s">
+        <v>9</v>
+      </c>
+      <c r="D121" s="1">
+        <v>11</v>
+      </c>
+      <c r="E121" t="s">
+        <v>9</v>
+      </c>
+      <c r="F121" s="1">
+        <v>18</v>
+      </c>
+      <c r="G121" t="s">
+        <v>9</v>
+      </c>
+      <c r="H121" s="1">
+        <v>23</v>
+      </c>
+      <c r="I121" t="s">
+        <v>9</v>
+      </c>
+      <c r="J121" s="1">
+        <v>9</v>
+      </c>
+      <c r="K121" t="s">
+        <v>9</v>
+      </c>
+      <c r="L121" s="1">
+        <v>10</v>
+      </c>
+      <c r="M121" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B122" s="1">
+        <v>3</v>
+      </c>
+      <c r="C122" t="s">
+        <v>9</v>
+      </c>
+      <c r="D122" s="1">
+        <v>11</v>
+      </c>
+      <c r="E122" t="s">
+        <v>9</v>
+      </c>
+      <c r="F122" s="1">
+        <v>18</v>
+      </c>
+      <c r="G122" t="s">
+        <v>9</v>
+      </c>
+      <c r="H122" s="1">
+        <v>23</v>
+      </c>
+      <c r="I122" t="s">
+        <v>9</v>
+      </c>
+      <c r="J122" s="1">
+        <v>2</v>
+      </c>
+      <c r="K122" t="s">
+        <v>9</v>
+      </c>
+      <c r="L122" s="1">
+        <v>21</v>
+      </c>
+      <c r="M122" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B123" s="1">
+        <v>3</v>
+      </c>
+      <c r="C123" t="s">
+        <v>9</v>
+      </c>
+      <c r="D123" s="1">
+        <v>11</v>
+      </c>
+      <c r="E123" t="s">
+        <v>9</v>
+      </c>
+      <c r="F123" s="1">
+        <v>18</v>
+      </c>
+      <c r="G123" t="s">
+        <v>9</v>
+      </c>
+      <c r="H123" s="1">
+        <v>23</v>
+      </c>
+      <c r="I123" t="s">
+        <v>9</v>
+      </c>
+      <c r="J123" s="1">
+        <v>5</v>
+      </c>
+      <c r="K123" t="s">
+        <v>9</v>
+      </c>
+      <c r="L123" s="1">
+        <v>13</v>
+      </c>
+      <c r="M123" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B124" s="1">
+        <v>3</v>
+      </c>
+      <c r="C124" t="s">
+        <v>9</v>
+      </c>
+      <c r="D124" s="1">
+        <v>11</v>
+      </c>
+      <c r="E124" t="s">
+        <v>9</v>
+      </c>
+      <c r="F124" s="1">
+        <v>18</v>
+      </c>
+      <c r="G124" t="s">
+        <v>9</v>
+      </c>
+      <c r="H124" s="1">
+        <v>23</v>
+      </c>
+      <c r="I124" t="s">
+        <v>9</v>
+      </c>
+      <c r="J124" s="1">
+        <v>12</v>
+      </c>
+      <c r="K124" t="s">
+        <v>9</v>
+      </c>
+      <c r="L124" s="1">
+        <v>24</v>
+      </c>
+      <c r="M124" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B125" s="1">
+        <v>2</v>
+      </c>
+      <c r="C125" t="s">
+        <v>9</v>
+      </c>
+      <c r="D125" s="1">
+        <v>8</v>
+      </c>
+      <c r="E125" t="s">
+        <v>9</v>
+      </c>
+      <c r="F125" s="1">
+        <v>12</v>
+      </c>
+      <c r="G125" t="s">
+        <v>9</v>
+      </c>
+      <c r="H125" s="1">
+        <v>15</v>
+      </c>
+      <c r="I125" t="s">
+        <v>9</v>
+      </c>
+      <c r="J125" s="1">
+        <v>3</v>
+      </c>
+      <c r="K125" t="s">
+        <v>9</v>
+      </c>
+      <c r="L125" s="1">
+        <v>14</v>
+      </c>
+      <c r="M125" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B126" s="1">
+        <v>2</v>
+      </c>
+      <c r="C126" t="s">
+        <v>9</v>
+      </c>
+      <c r="D126" s="1">
+        <v>8</v>
+      </c>
+      <c r="E126" t="s">
+        <v>9</v>
+      </c>
+      <c r="F126" s="1">
+        <v>12</v>
+      </c>
+      <c r="G126" t="s">
+        <v>9</v>
+      </c>
+      <c r="H126" s="1">
+        <v>15</v>
+      </c>
+      <c r="I126" t="s">
+        <v>9</v>
+      </c>
+      <c r="J126" s="1">
+        <v>18</v>
+      </c>
+      <c r="K126" t="s">
+        <v>9</v>
+      </c>
+      <c r="L126" s="1">
+        <v>22</v>
+      </c>
+      <c r="M126" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B127" s="1">
+        <v>2</v>
+      </c>
+      <c r="C127" t="s">
+        <v>9</v>
+      </c>
+      <c r="D127" s="1">
+        <v>8</v>
+      </c>
+      <c r="E127" t="s">
+        <v>9</v>
+      </c>
+      <c r="F127" s="1">
+        <v>12</v>
+      </c>
+      <c r="G127" t="s">
+        <v>9</v>
+      </c>
+      <c r="H127" s="1">
+        <v>15</v>
+      </c>
+      <c r="I127" t="s">
+        <v>9</v>
+      </c>
+      <c r="J127" s="1">
+        <v>16</v>
+      </c>
+      <c r="K127" t="s">
+        <v>9</v>
+      </c>
+      <c r="L127" s="1">
+        <v>13</v>
+      </c>
+      <c r="M127" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B128" s="1">
+        <v>2</v>
+      </c>
+      <c r="C128" t="s">
+        <v>9</v>
+      </c>
+      <c r="D128" s="1">
+        <v>8</v>
+      </c>
+      <c r="E128" t="s">
+        <v>9</v>
+      </c>
+      <c r="F128" s="1">
+        <v>12</v>
+      </c>
+      <c r="G128" t="s">
+        <v>9</v>
+      </c>
+      <c r="H128" s="1">
+        <v>15</v>
+      </c>
+      <c r="I128" t="s">
+        <v>9</v>
+      </c>
+      <c r="J128" s="1">
+        <v>13</v>
+      </c>
+      <c r="K128" t="s">
+        <v>9</v>
+      </c>
+      <c r="L128" s="1">
+        <v>20</v>
+      </c>
+      <c r="M128" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B129" s="1">
+        <v>2</v>
+      </c>
+      <c r="C129" t="s">
+        <v>9</v>
+      </c>
+      <c r="D129" s="1">
+        <v>8</v>
+      </c>
+      <c r="E129" t="s">
+        <v>9</v>
+      </c>
+      <c r="F129" s="1">
+        <v>12</v>
+      </c>
+      <c r="G129" t="s">
+        <v>9</v>
+      </c>
+      <c r="H129" s="1">
+        <v>15</v>
+      </c>
+      <c r="I129" t="s">
+        <v>9</v>
+      </c>
+      <c r="J129" s="1">
+        <v>4</v>
+      </c>
+      <c r="K129" t="s">
+        <v>9</v>
+      </c>
+      <c r="L129" s="1">
+        <v>23</v>
+      </c>
+      <c r="M129" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B130" s="1">
+        <v>2</v>
+      </c>
+      <c r="C130" t="s">
+        <v>9</v>
+      </c>
+      <c r="D130" s="1">
+        <v>8</v>
+      </c>
+      <c r="E130" t="s">
+        <v>9</v>
+      </c>
+      <c r="F130" s="1">
+        <v>12</v>
+      </c>
+      <c r="G130" t="s">
+        <v>9</v>
+      </c>
+      <c r="H130" s="1">
+        <v>15</v>
+      </c>
+      <c r="I130" t="s">
+        <v>9</v>
+      </c>
+      <c r="J130" s="1">
+        <v>9</v>
+      </c>
+      <c r="K130" t="s">
+        <v>9</v>
+      </c>
+      <c r="L130" s="1">
+        <v>10</v>
+      </c>
+      <c r="M130" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B131" s="1">
+        <v>2</v>
+      </c>
+      <c r="C131" t="s">
+        <v>9</v>
+      </c>
+      <c r="D131" s="1">
+        <v>8</v>
+      </c>
+      <c r="E131" t="s">
+        <v>9</v>
+      </c>
+      <c r="F131" s="1">
+        <v>12</v>
+      </c>
+      <c r="G131" t="s">
+        <v>9</v>
+      </c>
+      <c r="H131" s="1">
+        <v>15</v>
+      </c>
+      <c r="I131" t="s">
+        <v>9</v>
+      </c>
+      <c r="J131" s="1">
+        <v>11</v>
+      </c>
+      <c r="K131" t="s">
+        <v>9</v>
+      </c>
+      <c r="L131" s="1">
+        <v>20</v>
+      </c>
+      <c r="M131" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A132" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B132" s="1">
+        <v>2</v>
+      </c>
+      <c r="C132" t="s">
+        <v>9</v>
+      </c>
+      <c r="D132" s="1">
+        <v>8</v>
+      </c>
+      <c r="E132" t="s">
+        <v>9</v>
+      </c>
+      <c r="F132" s="1">
+        <v>12</v>
+      </c>
+      <c r="G132" t="s">
+        <v>9</v>
+      </c>
+      <c r="H132" s="1">
+        <v>15</v>
+      </c>
+      <c r="I132" t="s">
+        <v>9</v>
+      </c>
+      <c r="J132" s="1">
+        <v>5</v>
+      </c>
+      <c r="K132" t="s">
+        <v>9</v>
+      </c>
+      <c r="L132" s="1">
+        <v>13</v>
+      </c>
+      <c r="M132" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B133" s="1">
+        <v>2</v>
+      </c>
+      <c r="C133" t="s">
+        <v>9</v>
+      </c>
+      <c r="D133" s="1">
+        <v>8</v>
+      </c>
+      <c r="E133" t="s">
+        <v>9</v>
+      </c>
+      <c r="F133" s="1">
+        <v>12</v>
+      </c>
+      <c r="G133" t="s">
+        <v>9</v>
+      </c>
+      <c r="H133" s="1">
+        <v>15</v>
+      </c>
+      <c r="I133" t="s">
+        <v>9</v>
+      </c>
+      <c r="J133" s="1">
+        <v>17</v>
+      </c>
+      <c r="K133" t="s">
+        <v>9</v>
+      </c>
+      <c r="L133" s="1">
+        <v>18</v>
+      </c>
+      <c r="M133" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A134" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B134" s="1">
+        <v>2</v>
+      </c>
+      <c r="C134" t="s">
+        <v>9</v>
+      </c>
+      <c r="D134" s="1">
+        <v>5</v>
+      </c>
+      <c r="E134" t="s">
+        <v>9</v>
+      </c>
+      <c r="F134" s="1">
+        <v>13</v>
+      </c>
+      <c r="G134" t="s">
+        <v>9</v>
+      </c>
+      <c r="H134" s="1">
+        <v>25</v>
+      </c>
+      <c r="I134" t="s">
+        <v>9</v>
+      </c>
+      <c r="J134" s="1">
+        <v>7</v>
+      </c>
+      <c r="K134" t="s">
+        <v>9</v>
+      </c>
+      <c r="L134" s="1">
+        <v>8</v>
+      </c>
+      <c r="M134" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B135" s="1">
+        <v>2</v>
+      </c>
+      <c r="C135" t="s">
+        <v>9</v>
+      </c>
+      <c r="D135" s="1">
+        <v>5</v>
+      </c>
+      <c r="E135" t="s">
+        <v>9</v>
+      </c>
+      <c r="F135" s="1">
+        <v>13</v>
+      </c>
+      <c r="G135" t="s">
+        <v>9</v>
+      </c>
+      <c r="H135" s="1">
+        <v>25</v>
+      </c>
+      <c r="I135" t="s">
+        <v>9</v>
+      </c>
+      <c r="J135" s="1">
+        <v>3</v>
+      </c>
+      <c r="K135" t="s">
+        <v>9</v>
+      </c>
+      <c r="L135" s="1">
+        <v>14</v>
+      </c>
+      <c r="M135" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B136" s="1">
+        <v>2</v>
+      </c>
+      <c r="C136" t="s">
+        <v>9</v>
+      </c>
+      <c r="D136" s="1">
+        <v>5</v>
+      </c>
+      <c r="E136" t="s">
+        <v>9</v>
+      </c>
+      <c r="F136" s="1">
+        <v>13</v>
+      </c>
+      <c r="G136" t="s">
+        <v>9</v>
+      </c>
+      <c r="H136" s="1">
+        <v>25</v>
+      </c>
+      <c r="I136" t="s">
+        <v>9</v>
+      </c>
+      <c r="J136" s="1">
+        <v>18</v>
+      </c>
+      <c r="K136" t="s">
+        <v>9</v>
+      </c>
+      <c r="L136" s="1">
+        <v>22</v>
+      </c>
+      <c r="M136" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B137" s="1">
+        <v>2</v>
+      </c>
+      <c r="C137" t="s">
+        <v>9</v>
+      </c>
+      <c r="D137" s="1">
+        <v>5</v>
+      </c>
+      <c r="E137" t="s">
+        <v>9</v>
+      </c>
+      <c r="F137" s="1">
+        <v>13</v>
+      </c>
+      <c r="G137" t="s">
+        <v>9</v>
+      </c>
+      <c r="H137" s="1">
+        <v>25</v>
+      </c>
+      <c r="I137" t="s">
+        <v>9</v>
+      </c>
+      <c r="J137" s="1">
+        <v>16</v>
+      </c>
+      <c r="K137" t="s">
+        <v>9</v>
+      </c>
+      <c r="L137" s="1">
+        <v>24</v>
+      </c>
+      <c r="M137" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B138" s="1">
+        <v>2</v>
+      </c>
+      <c r="C138" t="s">
+        <v>9</v>
+      </c>
+      <c r="D138" s="1">
+        <v>5</v>
+      </c>
+      <c r="E138" t="s">
+        <v>9</v>
+      </c>
+      <c r="F138" s="1">
+        <v>13</v>
+      </c>
+      <c r="G138" t="s">
+        <v>9</v>
+      </c>
+      <c r="H138" s="1">
+        <v>25</v>
+      </c>
+      <c r="I138" t="s">
+        <v>9</v>
+      </c>
+      <c r="J138" s="1">
+        <v>4</v>
+      </c>
+      <c r="K138" t="s">
+        <v>9</v>
+      </c>
+      <c r="L138" s="1">
+        <v>23</v>
+      </c>
+      <c r="M138" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B139" s="1">
+        <v>2</v>
+      </c>
+      <c r="C139" t="s">
+        <v>9</v>
+      </c>
+      <c r="D139" s="1">
+        <v>5</v>
+      </c>
+      <c r="E139" t="s">
+        <v>9</v>
+      </c>
+      <c r="F139" s="1">
+        <v>13</v>
+      </c>
+      <c r="G139" t="s">
+        <v>9</v>
+      </c>
+      <c r="H139" s="1">
+        <v>25</v>
+      </c>
+      <c r="I139" t="s">
+        <v>9</v>
+      </c>
+      <c r="J139" s="1">
+        <v>15</v>
+      </c>
+      <c r="K139" t="s">
+        <v>9</v>
+      </c>
+      <c r="L139" s="1">
+        <v>19</v>
+      </c>
+      <c r="M139" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B140" s="1">
+        <v>2</v>
+      </c>
+      <c r="C140" t="s">
+        <v>9</v>
+      </c>
+      <c r="D140" s="1">
+        <v>5</v>
+      </c>
+      <c r="E140" t="s">
+        <v>9</v>
+      </c>
+      <c r="F140" s="1">
+        <v>13</v>
+      </c>
+      <c r="G140" t="s">
+        <v>9</v>
+      </c>
+      <c r="H140" s="1">
+        <v>25</v>
+      </c>
+      <c r="I140" t="s">
+        <v>9</v>
+      </c>
+      <c r="J140" s="1">
+        <v>9</v>
+      </c>
+      <c r="K140" t="s">
+        <v>9</v>
+      </c>
+      <c r="L140" s="1">
+        <v>10</v>
+      </c>
+      <c r="M140" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B141" s="1">
+        <v>2</v>
+      </c>
+      <c r="C141" t="s">
+        <v>9</v>
+      </c>
+      <c r="D141" s="1">
+        <v>5</v>
+      </c>
+      <c r="E141" t="s">
+        <v>9</v>
+      </c>
+      <c r="F141" s="1">
+        <v>13</v>
+      </c>
+      <c r="G141" t="s">
+        <v>9</v>
+      </c>
+      <c r="H141" s="1">
+        <v>25</v>
+      </c>
+      <c r="I141" t="s">
+        <v>9</v>
+      </c>
+      <c r="J141" s="1">
+        <v>11</v>
+      </c>
+      <c r="K141" t="s">
+        <v>9</v>
+      </c>
+      <c r="L141" s="1">
+        <v>20</v>
+      </c>
+      <c r="M141" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B142" s="1">
+        <v>2</v>
+      </c>
+      <c r="C142" t="s">
+        <v>9</v>
+      </c>
+      <c r="D142" s="1">
+        <v>5</v>
+      </c>
+      <c r="E142" t="s">
+        <v>9</v>
+      </c>
+      <c r="F142" s="1">
+        <v>13</v>
+      </c>
+      <c r="G142" t="s">
+        <v>9</v>
+      </c>
+      <c r="H142" s="1">
+        <v>25</v>
+      </c>
+      <c r="I142" t="s">
+        <v>9</v>
+      </c>
+      <c r="J142" s="1">
+        <v>17</v>
+      </c>
+      <c r="K142" t="s">
+        <v>9</v>
+      </c>
+      <c r="L142" s="1">
+        <v>18</v>
+      </c>
+      <c r="M142" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B143" s="1">
+        <v>2</v>
+      </c>
+      <c r="C143" t="s">
+        <v>9</v>
+      </c>
+      <c r="D143" s="1">
+        <v>5</v>
+      </c>
+      <c r="E143" t="s">
+        <v>9</v>
+      </c>
+      <c r="F143" s="1">
+        <v>13</v>
+      </c>
+      <c r="G143" t="s">
+        <v>9</v>
+      </c>
+      <c r="H143" s="1">
+        <v>25</v>
+      </c>
+      <c r="I143" t="s">
+        <v>9</v>
+      </c>
+      <c r="J143" s="1">
+        <v>12</v>
+      </c>
+      <c r="K143" t="s">
+        <v>9</v>
+      </c>
+      <c r="L143" s="1">
+        <v>24</v>
+      </c>
+      <c r="M143" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A144" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B144" s="1">
+        <v>2</v>
+      </c>
+      <c r="C144" t="s">
+        <v>9</v>
+      </c>
+      <c r="D144" s="1">
+        <v>4</v>
+      </c>
+      <c r="E144" t="s">
+        <v>9</v>
+      </c>
+      <c r="F144" s="1">
+        <v>7</v>
+      </c>
+      <c r="G144" t="s">
+        <v>9</v>
+      </c>
+      <c r="H144" s="1">
+        <v>14</v>
+      </c>
+      <c r="I144" t="s">
+        <v>9</v>
+      </c>
+      <c r="J144" s="1">
+        <v>18</v>
+      </c>
+      <c r="K144" t="s">
+        <v>9</v>
+      </c>
+      <c r="L144" s="1">
+        <v>22</v>
+      </c>
+      <c r="M144" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B145" s="1">
+        <v>2</v>
+      </c>
+      <c r="C145" t="s">
+        <v>9</v>
+      </c>
+      <c r="D145" s="1">
+        <v>4</v>
+      </c>
+      <c r="E145" t="s">
+        <v>9</v>
+      </c>
+      <c r="F145" s="1">
+        <v>7</v>
+      </c>
+      <c r="G145" t="s">
+        <v>9</v>
+      </c>
+      <c r="H145" s="1">
+        <v>14</v>
+      </c>
+      <c r="I145" t="s">
+        <v>9</v>
+      </c>
+      <c r="J145" s="1">
+        <v>16</v>
+      </c>
+      <c r="K145" t="s">
+        <v>9</v>
+      </c>
+      <c r="L145" s="1">
+        <v>24</v>
+      </c>
+      <c r="M145" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B146" s="1">
+        <v>2</v>
+      </c>
+      <c r="C146" t="s">
+        <v>9</v>
+      </c>
+      <c r="D146" s="1">
+        <v>4</v>
+      </c>
+      <c r="E146" t="s">
+        <v>9</v>
+      </c>
+      <c r="F146" s="1">
+        <v>7</v>
+      </c>
+      <c r="G146" t="s">
+        <v>9</v>
+      </c>
+      <c r="H146" s="1">
+        <v>14</v>
+      </c>
+      <c r="I146" t="s">
+        <v>9</v>
+      </c>
+      <c r="J146" s="1">
+        <v>13</v>
+      </c>
+      <c r="K146" t="s">
+        <v>9</v>
+      </c>
+      <c r="L146" s="1">
+        <v>20</v>
+      </c>
+      <c r="M146" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B147" s="1">
+        <v>2</v>
+      </c>
+      <c r="C147" t="s">
+        <v>9</v>
+      </c>
+      <c r="D147" s="1">
+        <v>4</v>
+      </c>
+      <c r="E147" t="s">
+        <v>9</v>
+      </c>
+      <c r="F147" s="1">
+        <v>7</v>
+      </c>
+      <c r="G147" t="s">
+        <v>9</v>
+      </c>
+      <c r="H147" s="1">
+        <v>14</v>
+      </c>
+      <c r="I147" t="s">
+        <v>9</v>
+      </c>
+      <c r="J147" s="1">
+        <v>15</v>
+      </c>
+      <c r="K147" t="s">
+        <v>9</v>
+      </c>
+      <c r="L147" s="1">
+        <v>19</v>
+      </c>
+      <c r="M147" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A148" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B148" s="1">
+        <v>2</v>
+      </c>
+      <c r="C148" t="s">
+        <v>9</v>
+      </c>
+      <c r="D148" s="1">
+        <v>4</v>
+      </c>
+      <c r="E148" t="s">
+        <v>9</v>
+      </c>
+      <c r="F148" s="1">
+        <v>7</v>
+      </c>
+      <c r="G148" t="s">
+        <v>9</v>
+      </c>
+      <c r="H148" s="1">
+        <v>14</v>
+      </c>
+      <c r="I148" t="s">
+        <v>9</v>
+      </c>
+      <c r="J148" s="1">
+        <v>12</v>
+      </c>
+      <c r="K148" t="s">
+        <v>9</v>
+      </c>
+      <c r="L148" s="1">
+        <v>25</v>
+      </c>
+      <c r="M148" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B149" s="1">
+        <v>2</v>
+      </c>
+      <c r="C149" t="s">
+        <v>9</v>
+      </c>
+      <c r="D149" s="1">
+        <v>4</v>
+      </c>
+      <c r="E149" t="s">
+        <v>9</v>
+      </c>
+      <c r="F149" s="1">
+        <v>7</v>
+      </c>
+      <c r="G149" t="s">
+        <v>9</v>
+      </c>
+      <c r="H149" s="1">
+        <v>14</v>
+      </c>
+      <c r="I149" t="s">
+        <v>9</v>
+      </c>
+      <c r="J149" s="1">
+        <v>9</v>
+      </c>
+      <c r="K149" t="s">
+        <v>9</v>
+      </c>
+      <c r="L149" s="1">
+        <v>10</v>
+      </c>
+      <c r="M149" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A150" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B150" s="1">
+        <v>2</v>
+      </c>
+      <c r="C150" t="s">
+        <v>9</v>
+      </c>
+      <c r="D150" s="1">
+        <v>4</v>
+      </c>
+      <c r="E150" t="s">
+        <v>9</v>
+      </c>
+      <c r="F150" s="1">
+        <v>7</v>
+      </c>
+      <c r="G150" t="s">
+        <v>9</v>
+      </c>
+      <c r="H150" s="1">
+        <v>14</v>
+      </c>
+      <c r="I150" t="s">
+        <v>9</v>
+      </c>
+      <c r="J150" s="1">
+        <v>11</v>
+      </c>
+      <c r="K150" t="s">
+        <v>9</v>
+      </c>
+      <c r="L150" s="1">
+        <v>20</v>
+      </c>
+      <c r="M150" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A151" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B151" s="1">
+        <v>2</v>
+      </c>
+      <c r="C151" t="s">
+        <v>9</v>
+      </c>
+      <c r="D151" s="1">
+        <v>4</v>
+      </c>
+      <c r="E151" t="s">
+        <v>9</v>
+      </c>
+      <c r="F151" s="1">
+        <v>7</v>
+      </c>
+      <c r="G151" t="s">
+        <v>9</v>
+      </c>
+      <c r="H151" s="1">
+        <v>14</v>
+      </c>
+      <c r="I151" t="s">
+        <v>9</v>
+      </c>
+      <c r="J151" s="1">
+        <v>5</v>
+      </c>
+      <c r="K151" t="s">
+        <v>9</v>
+      </c>
+      <c r="L151" s="1">
+        <v>13</v>
+      </c>
+      <c r="M151" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A152" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B152" s="1">
+        <v>2</v>
+      </c>
+      <c r="C152" t="s">
+        <v>9</v>
+      </c>
+      <c r="D152" s="1">
+        <v>4</v>
+      </c>
+      <c r="E152" t="s">
+        <v>9</v>
+      </c>
+      <c r="F152" s="1">
+        <v>7</v>
+      </c>
+      <c r="G152" t="s">
+        <v>9</v>
+      </c>
+      <c r="H152" s="1">
+        <v>14</v>
+      </c>
+      <c r="I152" t="s">
+        <v>9</v>
+      </c>
+      <c r="J152" s="1">
+        <v>17</v>
+      </c>
+      <c r="K152" t="s">
+        <v>9</v>
+      </c>
+      <c r="L152" s="1">
+        <v>18</v>
+      </c>
+      <c r="M152" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A153" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B153" s="1">
+        <v>2</v>
+      </c>
+      <c r="C153" t="s">
+        <v>9</v>
+      </c>
+      <c r="D153" s="1">
+        <v>4</v>
+      </c>
+      <c r="E153" t="s">
+        <v>9</v>
+      </c>
+      <c r="F153" s="1">
+        <v>7</v>
+      </c>
+      <c r="G153" t="s">
+        <v>9</v>
+      </c>
+      <c r="H153" s="1">
+        <v>14</v>
+      </c>
+      <c r="I153" t="s">
+        <v>9</v>
+      </c>
+      <c r="J153" s="1">
+        <v>12</v>
+      </c>
+      <c r="K153" t="s">
+        <v>9</v>
+      </c>
+      <c r="L153" s="1">
+        <v>24</v>
+      </c>
+      <c r="M153" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B154" s="1">
+        <v>1</v>
+      </c>
+      <c r="C154" t="s">
+        <v>9</v>
+      </c>
+      <c r="D154" s="1">
+        <v>12</v>
+      </c>
+      <c r="E154" t="s">
+        <v>9</v>
+      </c>
+      <c r="F154" s="1">
+        <v>13</v>
+      </c>
+      <c r="G154" t="s">
+        <v>9</v>
+      </c>
+      <c r="H154" s="1">
+        <v>14</v>
+      </c>
+      <c r="I154" t="s">
+        <v>9</v>
+      </c>
+      <c r="J154" s="1">
+        <v>7</v>
+      </c>
+      <c r="K154" t="s">
+        <v>9</v>
+      </c>
+      <c r="L154" s="1">
+        <v>8</v>
+      </c>
+      <c r="M154" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A155" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B155" s="1">
+        <v>1</v>
+      </c>
+      <c r="C155" t="s">
+        <v>9</v>
+      </c>
+      <c r="D155" s="1">
+        <v>12</v>
+      </c>
+      <c r="E155" t="s">
+        <v>9</v>
+      </c>
+      <c r="F155" s="1">
+        <v>13</v>
+      </c>
+      <c r="G155" t="s">
+        <v>9</v>
+      </c>
+      <c r="H155" s="1">
+        <v>14</v>
+      </c>
+      <c r="I155" t="s">
+        <v>9</v>
+      </c>
+      <c r="J155" s="1">
+        <v>18</v>
+      </c>
+      <c r="K155" t="s">
+        <v>9</v>
+      </c>
+      <c r="L155" s="1">
+        <v>22</v>
+      </c>
+      <c r="M155" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B156" s="1">
+        <v>1</v>
+      </c>
+      <c r="C156" t="s">
+        <v>9</v>
+      </c>
+      <c r="D156" s="1">
+        <v>12</v>
+      </c>
+      <c r="E156" t="s">
+        <v>9</v>
+      </c>
+      <c r="F156" s="1">
+        <v>13</v>
+      </c>
+      <c r="G156" t="s">
+        <v>9</v>
+      </c>
+      <c r="H156" s="1">
+        <v>14</v>
+      </c>
+      <c r="I156" t="s">
+        <v>9</v>
+      </c>
+      <c r="J156" s="1">
+        <v>16</v>
+      </c>
+      <c r="K156" t="s">
+        <v>9</v>
+      </c>
+      <c r="L156" s="1">
+        <v>24</v>
+      </c>
+      <c r="M156" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B157" s="1">
+        <v>1</v>
+      </c>
+      <c r="C157" t="s">
+        <v>9</v>
+      </c>
+      <c r="D157" s="1">
+        <v>12</v>
+      </c>
+      <c r="E157" t="s">
+        <v>9</v>
+      </c>
+      <c r="F157" s="1">
+        <v>13</v>
+      </c>
+      <c r="G157" t="s">
+        <v>9</v>
+      </c>
+      <c r="H157" s="1">
+        <v>14</v>
+      </c>
+      <c r="I157" t="s">
+        <v>9</v>
+      </c>
+      <c r="J157" s="1">
+        <v>4</v>
+      </c>
+      <c r="K157" t="s">
+        <v>9</v>
+      </c>
+      <c r="L157" s="1">
+        <v>23</v>
+      </c>
+      <c r="M157" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A158" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B158" s="1">
+        <v>1</v>
+      </c>
+      <c r="C158" t="s">
+        <v>9</v>
+      </c>
+      <c r="D158" s="1">
+        <v>12</v>
+      </c>
+      <c r="E158" t="s">
+        <v>9</v>
+      </c>
+      <c r="F158" s="1">
+        <v>13</v>
+      </c>
+      <c r="G158" t="s">
+        <v>9</v>
+      </c>
+      <c r="H158" s="1">
+        <v>14</v>
+      </c>
+      <c r="I158" t="s">
+        <v>9</v>
+      </c>
+      <c r="J158" s="1">
+        <v>15</v>
+      </c>
+      <c r="K158" t="s">
+        <v>9</v>
+      </c>
+      <c r="L158" s="1">
+        <v>19</v>
+      </c>
+      <c r="M158" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A159" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B159" s="1">
+        <v>1</v>
+      </c>
+      <c r="C159" t="s">
+        <v>9</v>
+      </c>
+      <c r="D159" s="1">
+        <v>12</v>
+      </c>
+      <c r="E159" t="s">
+        <v>9</v>
+      </c>
+      <c r="F159" s="1">
+        <v>13</v>
+      </c>
+      <c r="G159" t="s">
+        <v>9</v>
+      </c>
+      <c r="H159" s="1">
+        <v>14</v>
+      </c>
+      <c r="I159" t="s">
+        <v>9</v>
+      </c>
+      <c r="J159" s="1">
+        <v>9</v>
+      </c>
+      <c r="K159" t="s">
+        <v>9</v>
+      </c>
+      <c r="L159" s="1">
+        <v>10</v>
+      </c>
+      <c r="M159" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A160" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B160" s="1">
+        <v>1</v>
+      </c>
+      <c r="C160" t="s">
+        <v>9</v>
+      </c>
+      <c r="D160" s="1">
+        <v>12</v>
+      </c>
+      <c r="E160" t="s">
+        <v>9</v>
+      </c>
+      <c r="F160" s="1">
+        <v>13</v>
+      </c>
+      <c r="G160" t="s">
+        <v>9</v>
+      </c>
+      <c r="H160" s="1">
+        <v>14</v>
+      </c>
+      <c r="I160" t="s">
+        <v>9</v>
+      </c>
+      <c r="J160" s="1">
+        <v>11</v>
+      </c>
+      <c r="K160" t="s">
+        <v>9</v>
+      </c>
+      <c r="L160" s="1">
+        <v>20</v>
+      </c>
+      <c r="M160" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A161" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B161" s="1">
+        <v>1</v>
+      </c>
+      <c r="C161" t="s">
+        <v>9</v>
+      </c>
+      <c r="D161" s="1">
+        <v>12</v>
+      </c>
+      <c r="E161" t="s">
+        <v>9</v>
+      </c>
+      <c r="F161" s="1">
+        <v>13</v>
+      </c>
+      <c r="G161" t="s">
+        <v>9</v>
+      </c>
+      <c r="H161" s="1">
+        <v>14</v>
+      </c>
+      <c r="I161" t="s">
+        <v>9</v>
+      </c>
+      <c r="J161" s="1">
+        <v>2</v>
+      </c>
+      <c r="K161" t="s">
+        <v>9</v>
+      </c>
+      <c r="L161" s="1">
+        <v>21</v>
+      </c>
+      <c r="M161" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A162" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B162" s="1">
+        <v>1</v>
+      </c>
+      <c r="C162" t="s">
+        <v>9</v>
+      </c>
+      <c r="D162" s="1">
+        <v>12</v>
+      </c>
+      <c r="E162" t="s">
+        <v>9</v>
+      </c>
+      <c r="F162" s="1">
+        <v>13</v>
+      </c>
+      <c r="G162" t="s">
+        <v>9</v>
+      </c>
+      <c r="H162" s="1">
+        <v>14</v>
+      </c>
+      <c r="I162" t="s">
+        <v>9</v>
+      </c>
+      <c r="J162" s="1">
+        <v>17</v>
+      </c>
+      <c r="K162" t="s">
+        <v>9</v>
+      </c>
+      <c r="L162" s="1">
+        <v>18</v>
+      </c>
+      <c r="M162" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A163" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B163" s="1">
+        <v>1</v>
+      </c>
+      <c r="C163" t="s">
+        <v>9</v>
+      </c>
+      <c r="D163" s="1">
+        <v>5</v>
+      </c>
+      <c r="E163" t="s">
+        <v>9</v>
+      </c>
+      <c r="F163" s="1">
+        <v>7</v>
+      </c>
+      <c r="G163" t="s">
+        <v>9</v>
+      </c>
+      <c r="H163" s="1">
+        <v>8</v>
+      </c>
+      <c r="I163" t="s">
+        <v>9</v>
+      </c>
+      <c r="J163" s="1">
+        <v>3</v>
+      </c>
+      <c r="K163" t="s">
+        <v>9</v>
+      </c>
+      <c r="L163" s="1">
+        <v>14</v>
+      </c>
+      <c r="M163" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A164" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B164" s="1">
+        <v>1</v>
+      </c>
+      <c r="C164" t="s">
+        <v>9</v>
+      </c>
+      <c r="D164" s="1">
+        <v>5</v>
+      </c>
+      <c r="E164" t="s">
+        <v>9</v>
+      </c>
+      <c r="F164" s="1">
+        <v>7</v>
+      </c>
+      <c r="G164" t="s">
+        <v>9</v>
+      </c>
+      <c r="H164" s="1">
+        <v>8</v>
+      </c>
+      <c r="I164" t="s">
+        <v>9</v>
+      </c>
+      <c r="J164" s="1">
+        <v>18</v>
+      </c>
+      <c r="K164" t="s">
+        <v>9</v>
+      </c>
+      <c r="L164" s="1">
+        <v>22</v>
+      </c>
+      <c r="M164" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A165" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B165" s="1">
+        <v>1</v>
+      </c>
+      <c r="C165" t="s">
+        <v>9</v>
+      </c>
+      <c r="D165" s="1">
+        <v>5</v>
+      </c>
+      <c r="E165" t="s">
+        <v>9</v>
+      </c>
+      <c r="F165" s="1">
+        <v>7</v>
+      </c>
+      <c r="G165" t="s">
+        <v>9</v>
+      </c>
+      <c r="H165" s="1">
+        <v>8</v>
+      </c>
+      <c r="I165" t="s">
+        <v>9</v>
+      </c>
+      <c r="J165" s="1">
+        <v>16</v>
+      </c>
+      <c r="K165" t="s">
+        <v>9</v>
+      </c>
+      <c r="L165" s="1">
+        <v>24</v>
+      </c>
+      <c r="M165" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A166" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B166" s="1">
+        <v>1</v>
+      </c>
+      <c r="C166" t="s">
+        <v>9</v>
+      </c>
+      <c r="D166" s="1">
+        <v>5</v>
+      </c>
+      <c r="E166" t="s">
+        <v>9</v>
+      </c>
+      <c r="F166" s="1">
+        <v>7</v>
+      </c>
+      <c r="G166" t="s">
+        <v>9</v>
+      </c>
+      <c r="H166" s="1">
+        <v>8</v>
+      </c>
+      <c r="I166" t="s">
+        <v>9</v>
+      </c>
+      <c r="J166" s="1">
+        <v>13</v>
+      </c>
+      <c r="K166" t="s">
+        <v>9</v>
+      </c>
+      <c r="L166" s="1">
+        <v>20</v>
+      </c>
+      <c r="M166" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A167" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B167" s="1">
+        <v>1</v>
+      </c>
+      <c r="C167" t="s">
+        <v>9</v>
+      </c>
+      <c r="D167" s="1">
+        <v>5</v>
+      </c>
+      <c r="E167" t="s">
+        <v>9</v>
+      </c>
+      <c r="F167" s="1">
+        <v>7</v>
+      </c>
+      <c r="G167" t="s">
+        <v>9</v>
+      </c>
+      <c r="H167" s="1">
+        <v>8</v>
+      </c>
+      <c r="I167" t="s">
+        <v>9</v>
+      </c>
+      <c r="J167" s="1">
+        <v>4</v>
+      </c>
+      <c r="K167" t="s">
+        <v>9</v>
+      </c>
+      <c r="L167" s="1">
+        <v>23</v>
+      </c>
+      <c r="M167" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A168" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B168" s="1">
+        <v>1</v>
+      </c>
+      <c r="C168" t="s">
+        <v>9</v>
+      </c>
+      <c r="D168" s="1">
+        <v>5</v>
+      </c>
+      <c r="E168" t="s">
+        <v>9</v>
+      </c>
+      <c r="F168" s="1">
+        <v>7</v>
+      </c>
+      <c r="G168" t="s">
+        <v>9</v>
+      </c>
+      <c r="H168" s="1">
+        <v>8</v>
+      </c>
+      <c r="I168" t="s">
+        <v>9</v>
+      </c>
+      <c r="J168" s="1">
+        <v>15</v>
+      </c>
+      <c r="K168" t="s">
+        <v>9</v>
+      </c>
+      <c r="L168" s="1">
+        <v>19</v>
+      </c>
+      <c r="M168" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A169" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B169" s="1">
+        <v>1</v>
+      </c>
+      <c r="C169" t="s">
+        <v>9</v>
+      </c>
+      <c r="D169" s="1">
+        <v>5</v>
+      </c>
+      <c r="E169" t="s">
+        <v>9</v>
+      </c>
+      <c r="F169" s="1">
+        <v>7</v>
+      </c>
+      <c r="G169" t="s">
+        <v>9</v>
+      </c>
+      <c r="H169" s="1">
+        <v>8</v>
+      </c>
+      <c r="I169" t="s">
+        <v>9</v>
+      </c>
+      <c r="J169" s="1">
+        <v>12</v>
+      </c>
+      <c r="K169" t="s">
+        <v>9</v>
+      </c>
+      <c r="L169" s="1">
+        <v>25</v>
+      </c>
+      <c r="M169" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A170" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B170" s="1">
+        <v>1</v>
+      </c>
+      <c r="C170" t="s">
+        <v>9</v>
+      </c>
+      <c r="D170" s="1">
+        <v>5</v>
+      </c>
+      <c r="E170" t="s">
+        <v>9</v>
+      </c>
+      <c r="F170" s="1">
+        <v>7</v>
+      </c>
+      <c r="G170" t="s">
+        <v>9</v>
+      </c>
+      <c r="H170" s="1">
+        <v>8</v>
+      </c>
+      <c r="I170" t="s">
+        <v>9</v>
+      </c>
+      <c r="J170" s="1">
+        <v>9</v>
+      </c>
+      <c r="K170" t="s">
+        <v>9</v>
+      </c>
+      <c r="L170" s="1">
+        <v>10</v>
+      </c>
+      <c r="M170" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A171" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B171" s="1">
+        <v>1</v>
+      </c>
+      <c r="C171" t="s">
+        <v>9</v>
+      </c>
+      <c r="D171" s="1">
+        <v>5</v>
+      </c>
+      <c r="E171" t="s">
+        <v>9</v>
+      </c>
+      <c r="F171" s="1">
+        <v>7</v>
+      </c>
+      <c r="G171" t="s">
+        <v>9</v>
+      </c>
+      <c r="H171" s="1">
+        <v>8</v>
+      </c>
+      <c r="I171" t="s">
+        <v>9</v>
+      </c>
+      <c r="J171" s="1">
+        <v>11</v>
+      </c>
+      <c r="K171" t="s">
+        <v>9</v>
+      </c>
+      <c r="L171" s="1">
+        <v>20</v>
+      </c>
+      <c r="M171" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A172" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B172" s="1">
+        <v>1</v>
+      </c>
+      <c r="C172" t="s">
+        <v>9</v>
+      </c>
+      <c r="D172" s="1">
+        <v>5</v>
+      </c>
+      <c r="E172" t="s">
+        <v>9</v>
+      </c>
+      <c r="F172" s="1">
+        <v>7</v>
+      </c>
+      <c r="G172" t="s">
+        <v>9</v>
+      </c>
+      <c r="H172" s="1">
+        <v>8</v>
+      </c>
+      <c r="I172" t="s">
+        <v>9</v>
+      </c>
+      <c r="J172" s="1">
+        <v>2</v>
+      </c>
+      <c r="K172" t="s">
+        <v>9</v>
+      </c>
+      <c r="L172" s="1">
+        <v>21</v>
+      </c>
+      <c r="M172" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A173" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B173" s="1">
+        <v>1</v>
+      </c>
+      <c r="C173" t="s">
+        <v>9</v>
+      </c>
+      <c r="D173" s="1">
+        <v>5</v>
+      </c>
+      <c r="E173" t="s">
+        <v>9</v>
+      </c>
+      <c r="F173" s="1">
+        <v>7</v>
+      </c>
+      <c r="G173" t="s">
+        <v>9</v>
+      </c>
+      <c r="H173" s="1">
+        <v>8</v>
+      </c>
+      <c r="I173" t="s">
+        <v>9</v>
+      </c>
+      <c r="J173" s="1">
+        <v>17</v>
+      </c>
+      <c r="K173" t="s">
+        <v>9</v>
+      </c>
+      <c r="L173" s="1">
+        <v>18</v>
+      </c>
+      <c r="M173" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A174" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B174" s="1">
+        <v>1</v>
+      </c>
+      <c r="C174" t="s">
+        <v>9</v>
+      </c>
+      <c r="D174" s="1">
+        <v>5</v>
+      </c>
+      <c r="E174" t="s">
+        <v>9</v>
+      </c>
+      <c r="F174" s="1">
+        <v>7</v>
+      </c>
+      <c r="G174" t="s">
+        <v>9</v>
+      </c>
+      <c r="H174" s="1">
+        <v>8</v>
+      </c>
+      <c r="I174" t="s">
+        <v>9</v>
+      </c>
+      <c r="J174" s="1">
+        <v>12</v>
+      </c>
+      <c r="K174" t="s">
+        <v>9</v>
+      </c>
+      <c r="L174" s="1">
+        <v>24</v>
+      </c>
+      <c r="M174" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A175" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B175" s="1">
+        <v>1</v>
+      </c>
+      <c r="C175" t="s">
+        <v>9</v>
+      </c>
+      <c r="D175" s="1">
+        <v>4</v>
+      </c>
+      <c r="E175" t="s">
+        <v>9</v>
+      </c>
+      <c r="F175" s="1">
+        <v>15</v>
+      </c>
+      <c r="G175" t="s">
+        <v>9</v>
+      </c>
+      <c r="H175" s="1">
+        <v>25</v>
+      </c>
+      <c r="I175" t="s">
+        <v>9</v>
+      </c>
+      <c r="J175" s="1">
+        <v>7</v>
+      </c>
+      <c r="K175" t="s">
+        <v>9</v>
+      </c>
+      <c r="L175" s="1">
+        <v>8</v>
+      </c>
+      <c r="M175" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A176" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B176" s="1">
+        <v>1</v>
+      </c>
+      <c r="C176" t="s">
+        <v>9</v>
+      </c>
+      <c r="D176" s="1">
+        <v>4</v>
+      </c>
+      <c r="E176" t="s">
+        <v>9</v>
+      </c>
+      <c r="F176" s="1">
+        <v>15</v>
+      </c>
+      <c r="G176" t="s">
+        <v>9</v>
+      </c>
+      <c r="H176" s="1">
+        <v>25</v>
+      </c>
+      <c r="I176" t="s">
+        <v>9</v>
+      </c>
+      <c r="J176" s="1">
+        <v>3</v>
+      </c>
+      <c r="K176" t="s">
+        <v>9</v>
+      </c>
+      <c r="L176" s="1">
+        <v>14</v>
+      </c>
+      <c r="M176" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A177" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B177" s="1">
+        <v>1</v>
+      </c>
+      <c r="C177" t="s">
+        <v>9</v>
+      </c>
+      <c r="D177" s="1">
+        <v>4</v>
+      </c>
+      <c r="E177" t="s">
+        <v>9</v>
+      </c>
+      <c r="F177" s="1">
+        <v>15</v>
+      </c>
+      <c r="G177" t="s">
+        <v>9</v>
+      </c>
+      <c r="H177" s="1">
+        <v>25</v>
+      </c>
+      <c r="I177" t="s">
+        <v>9</v>
+      </c>
+      <c r="J177" s="1">
+        <v>18</v>
+      </c>
+      <c r="K177" t="s">
+        <v>9</v>
+      </c>
+      <c r="L177" s="1">
+        <v>22</v>
+      </c>
+      <c r="M177" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A178" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B178" s="1">
+        <v>1</v>
+      </c>
+      <c r="C178" t="s">
+        <v>9</v>
+      </c>
+      <c r="D178" s="1">
+        <v>4</v>
+      </c>
+      <c r="E178" t="s">
+        <v>9</v>
+      </c>
+      <c r="F178" s="1">
+        <v>15</v>
+      </c>
+      <c r="G178" t="s">
+        <v>9</v>
+      </c>
+      <c r="H178" s="1">
+        <v>25</v>
+      </c>
+      <c r="I178" t="s">
+        <v>9</v>
+      </c>
+      <c r="J178" s="1">
+        <v>16</v>
+      </c>
+      <c r="K178" t="s">
+        <v>9</v>
+      </c>
+      <c r="L178" s="1">
+        <v>24</v>
+      </c>
+      <c r="M178" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A179" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B179" s="1">
+        <v>1</v>
+      </c>
+      <c r="C179" t="s">
+        <v>9</v>
+      </c>
+      <c r="D179" s="1">
+        <v>4</v>
+      </c>
+      <c r="E179" t="s">
+        <v>9</v>
+      </c>
+      <c r="F179" s="1">
+        <v>15</v>
+      </c>
+      <c r="G179" t="s">
+        <v>9</v>
+      </c>
+      <c r="H179" s="1">
+        <v>25</v>
+      </c>
+      <c r="I179" t="s">
+        <v>9</v>
+      </c>
+      <c r="J179" s="1">
+        <v>13</v>
+      </c>
+      <c r="K179" t="s">
+        <v>9</v>
+      </c>
+      <c r="L179" s="1">
+        <v>20</v>
+      </c>
+      <c r="M179" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A180" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B180" s="1">
+        <v>1</v>
+      </c>
+      <c r="C180" t="s">
+        <v>9</v>
+      </c>
+      <c r="D180" s="1">
+        <v>4</v>
+      </c>
+      <c r="E180" t="s">
+        <v>9</v>
+      </c>
+      <c r="F180" s="1">
+        <v>15</v>
+      </c>
+      <c r="G180" t="s">
+        <v>9</v>
+      </c>
+      <c r="H180" s="1">
+        <v>25</v>
+      </c>
+      <c r="I180" t="s">
+        <v>9</v>
+      </c>
+      <c r="J180" s="1">
+        <v>9</v>
+      </c>
+      <c r="K180" t="s">
+        <v>9</v>
+      </c>
+      <c r="L180" s="1">
+        <v>10</v>
+      </c>
+      <c r="M180" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A181" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B181" s="1">
+        <v>1</v>
+      </c>
+      <c r="C181" t="s">
+        <v>9</v>
+      </c>
+      <c r="D181" s="1">
+        <v>4</v>
+      </c>
+      <c r="E181" t="s">
+        <v>9</v>
+      </c>
+      <c r="F181" s="1">
+        <v>15</v>
+      </c>
+      <c r="G181" t="s">
+        <v>9</v>
+      </c>
+      <c r="H181" s="1">
+        <v>25</v>
+      </c>
+      <c r="I181" t="s">
+        <v>9</v>
+      </c>
+      <c r="J181" s="1">
+        <v>11</v>
+      </c>
+      <c r="K181" t="s">
+        <v>9</v>
+      </c>
+      <c r="L181" s="1">
+        <v>20</v>
+      </c>
+      <c r="M181" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A182" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B182" s="1">
+        <v>1</v>
+      </c>
+      <c r="C182" t="s">
+        <v>9</v>
+      </c>
+      <c r="D182" s="1">
+        <v>4</v>
+      </c>
+      <c r="E182" t="s">
+        <v>9</v>
+      </c>
+      <c r="F182" s="1">
+        <v>15</v>
+      </c>
+      <c r="G182" t="s">
+        <v>9</v>
+      </c>
+      <c r="H182" s="1">
+        <v>25</v>
+      </c>
+      <c r="I182" t="s">
+        <v>9</v>
+      </c>
+      <c r="J182" s="1">
+        <v>2</v>
+      </c>
+      <c r="K182" t="s">
+        <v>9</v>
+      </c>
+      <c r="L182" s="1">
+        <v>21</v>
+      </c>
+      <c r="M182" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A183" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B183" s="1">
+        <v>1</v>
+      </c>
+      <c r="C183" t="s">
+        <v>9</v>
+      </c>
+      <c r="D183" s="1">
+        <v>4</v>
+      </c>
+      <c r="E183" t="s">
+        <v>9</v>
+      </c>
+      <c r="F183" s="1">
+        <v>15</v>
+      </c>
+      <c r="G183" t="s">
+        <v>9</v>
+      </c>
+      <c r="H183" s="1">
+        <v>25</v>
+      </c>
+      <c r="I183" t="s">
+        <v>9</v>
+      </c>
+      <c r="J183" s="1">
+        <v>5</v>
+      </c>
+      <c r="K183" t="s">
+        <v>9</v>
+      </c>
+      <c r="L183" s="1">
+        <v>13</v>
+      </c>
+      <c r="M183" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A184" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B184" s="1">
+        <v>1</v>
+      </c>
+      <c r="C184" t="s">
+        <v>9</v>
+      </c>
+      <c r="D184" s="1">
+        <v>4</v>
+      </c>
+      <c r="E184" t="s">
+        <v>9</v>
+      </c>
+      <c r="F184" s="1">
+        <v>15</v>
+      </c>
+      <c r="G184" t="s">
+        <v>9</v>
+      </c>
+      <c r="H184" s="1">
+        <v>25</v>
+      </c>
+      <c r="I184" t="s">
+        <v>9</v>
+      </c>
+      <c r="J184" s="1">
+        <v>17</v>
+      </c>
+      <c r="K184" t="s">
+        <v>9</v>
+      </c>
+      <c r="L184" s="1">
+        <v>18</v>
+      </c>
+      <c r="M184" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A185" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B185" s="1">
+        <v>1</v>
+      </c>
+      <c r="C185" t="s">
+        <v>9</v>
+      </c>
+      <c r="D185" s="1">
+        <v>4</v>
+      </c>
+      <c r="E185" t="s">
+        <v>9</v>
+      </c>
+      <c r="F185" s="1">
+        <v>15</v>
+      </c>
+      <c r="G185" t="s">
+        <v>9</v>
+      </c>
+      <c r="H185" s="1">
+        <v>25</v>
+      </c>
+      <c r="I185" t="s">
+        <v>9</v>
+      </c>
+      <c r="J185" s="1">
+        <v>12</v>
+      </c>
+      <c r="K185" t="s">
+        <v>9</v>
+      </c>
+      <c r="L185" s="1">
+        <v>24</v>
+      </c>
+      <c r="M185" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A186" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B186" s="1">
+        <v>1</v>
+      </c>
+      <c r="C186" t="s">
+        <v>9</v>
+      </c>
+      <c r="D186" s="1">
+        <v>2</v>
+      </c>
+      <c r="E186" t="s">
+        <v>9</v>
+      </c>
+      <c r="F186" s="1">
+        <v>10</v>
+      </c>
+      <c r="G186" t="s">
+        <v>9</v>
+      </c>
+      <c r="H186" s="1">
+        <v>16</v>
+      </c>
+      <c r="I186" t="s">
+        <v>9</v>
+      </c>
+      <c r="J186" s="1">
+        <v>7</v>
+      </c>
+      <c r="K186" t="s">
+        <v>9</v>
+      </c>
+      <c r="L186" s="1">
+        <v>8</v>
+      </c>
+      <c r="M186" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A187" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B187" s="1">
+        <v>1</v>
+      </c>
+      <c r="C187" t="s">
+        <v>9</v>
+      </c>
+      <c r="D187" s="1">
+        <v>2</v>
+      </c>
+      <c r="E187" t="s">
+        <v>9</v>
+      </c>
+      <c r="F187" s="1">
+        <v>10</v>
+      </c>
+      <c r="G187" t="s">
+        <v>9</v>
+      </c>
+      <c r="H187" s="1">
+        <v>16</v>
+      </c>
+      <c r="I187" t="s">
+        <v>9</v>
+      </c>
+      <c r="J187" s="1">
+        <v>3</v>
+      </c>
+      <c r="K187" t="s">
+        <v>9</v>
+      </c>
+      <c r="L187" s="1">
+        <v>14</v>
+      </c>
+      <c r="M187" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A188" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B188" s="1">
+        <v>1</v>
+      </c>
+      <c r="C188" t="s">
+        <v>9</v>
+      </c>
+      <c r="D188" s="1">
+        <v>2</v>
+      </c>
+      <c r="E188" t="s">
+        <v>9</v>
+      </c>
+      <c r="F188" s="1">
+        <v>10</v>
+      </c>
+      <c r="G188" t="s">
+        <v>9</v>
+      </c>
+      <c r="H188" s="1">
+        <v>16</v>
+      </c>
+      <c r="I188" t="s">
+        <v>9</v>
+      </c>
+      <c r="J188" s="1">
+        <v>18</v>
+      </c>
+      <c r="K188" t="s">
+        <v>9</v>
+      </c>
+      <c r="L188" s="1">
+        <v>22</v>
+      </c>
+      <c r="M188" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A189" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B189" s="1">
+        <v>1</v>
+      </c>
+      <c r="C189" t="s">
+        <v>9</v>
+      </c>
+      <c r="D189" s="1">
+        <v>2</v>
+      </c>
+      <c r="E189" t="s">
+        <v>9</v>
+      </c>
+      <c r="F189" s="1">
+        <v>10</v>
+      </c>
+      <c r="G189" t="s">
+        <v>9</v>
+      </c>
+      <c r="H189" s="1">
+        <v>16</v>
+      </c>
+      <c r="I189" t="s">
+        <v>9</v>
+      </c>
+      <c r="J189" s="1">
+        <v>13</v>
+      </c>
+      <c r="K189" t="s">
+        <v>9</v>
+      </c>
+      <c r="L189" s="1">
+        <v>20</v>
+      </c>
+      <c r="M189" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A190" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B190" s="1">
+        <v>1</v>
+      </c>
+      <c r="C190" t="s">
+        <v>9</v>
+      </c>
+      <c r="D190" s="1">
+        <v>2</v>
+      </c>
+      <c r="E190" t="s">
+        <v>9</v>
+      </c>
+      <c r="F190" s="1">
+        <v>10</v>
+      </c>
+      <c r="G190" t="s">
+        <v>9</v>
+      </c>
+      <c r="H190" s="1">
+        <v>16</v>
+      </c>
+      <c r="I190" t="s">
+        <v>9</v>
+      </c>
+      <c r="J190" s="1">
+        <v>4</v>
+      </c>
+      <c r="K190" t="s">
+        <v>9</v>
+      </c>
+      <c r="L190" s="1">
+        <v>23</v>
+      </c>
+      <c r="M190" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A191" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B191" s="1">
+        <v>1</v>
+      </c>
+      <c r="C191" t="s">
+        <v>9</v>
+      </c>
+      <c r="D191" s="1">
+        <v>2</v>
+      </c>
+      <c r="E191" t="s">
+        <v>9</v>
+      </c>
+      <c r="F191" s="1">
+        <v>10</v>
+      </c>
+      <c r="G191" t="s">
+        <v>9</v>
+      </c>
+      <c r="H191" s="1">
+        <v>16</v>
+      </c>
+      <c r="I191" t="s">
+        <v>9</v>
+      </c>
+      <c r="J191" s="1">
+        <v>15</v>
+      </c>
+      <c r="K191" t="s">
+        <v>9</v>
+      </c>
+      <c r="L191" s="1">
+        <v>19</v>
+      </c>
+      <c r="M191" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A192" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B192" s="1">
+        <v>1</v>
+      </c>
+      <c r="C192" t="s">
+        <v>9</v>
+      </c>
+      <c r="D192" s="1">
+        <v>2</v>
+      </c>
+      <c r="E192" t="s">
+        <v>9</v>
+      </c>
+      <c r="F192" s="1">
+        <v>10</v>
+      </c>
+      <c r="G192" t="s">
+        <v>9</v>
+      </c>
+      <c r="H192" s="1">
+        <v>16</v>
+      </c>
+      <c r="I192" t="s">
+        <v>9</v>
+      </c>
+      <c r="J192" s="1">
+        <v>12</v>
+      </c>
+      <c r="K192" t="s">
+        <v>9</v>
+      </c>
+      <c r="L192" s="1">
+        <v>25</v>
+      </c>
+      <c r="M192" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A193" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B193" s="1">
+        <v>1</v>
+      </c>
+      <c r="C193" t="s">
+        <v>9</v>
+      </c>
+      <c r="D193" s="1">
+        <v>2</v>
+      </c>
+      <c r="E193" t="s">
+        <v>9</v>
+      </c>
+      <c r="F193" s="1">
+        <v>10</v>
+      </c>
+      <c r="G193" t="s">
+        <v>9</v>
+      </c>
+      <c r="H193" s="1">
+        <v>16</v>
+      </c>
+      <c r="I193" t="s">
+        <v>9</v>
+      </c>
+      <c r="J193" s="1">
+        <v>11</v>
+      </c>
+      <c r="K193" t="s">
+        <v>9</v>
+      </c>
+      <c r="L193" s="1">
+        <v>20</v>
+      </c>
+      <c r="M193" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A194" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B194" s="1">
+        <v>1</v>
+      </c>
+      <c r="C194" t="s">
+        <v>9</v>
+      </c>
+      <c r="D194" s="1">
+        <v>2</v>
+      </c>
+      <c r="E194" t="s">
+        <v>9</v>
+      </c>
+      <c r="F194" s="1">
+        <v>10</v>
+      </c>
+      <c r="G194" t="s">
+        <v>9</v>
+      </c>
+      <c r="H194" s="1">
+        <v>16</v>
+      </c>
+      <c r="I194" t="s">
+        <v>9</v>
+      </c>
+      <c r="J194" s="1">
+        <v>5</v>
+      </c>
+      <c r="K194" t="s">
+        <v>9</v>
+      </c>
+      <c r="L194" s="1">
+        <v>13</v>
+      </c>
+      <c r="M194" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A195" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B195" s="1">
+        <v>1</v>
+      </c>
+      <c r="C195" t="s">
+        <v>9</v>
+      </c>
+      <c r="D195" s="1">
+        <v>2</v>
+      </c>
+      <c r="E195" t="s">
+        <v>9</v>
+      </c>
+      <c r="F195" s="1">
+        <v>10</v>
+      </c>
+      <c r="G195" t="s">
+        <v>9</v>
+      </c>
+      <c r="H195" s="1">
+        <v>16</v>
+      </c>
+      <c r="I195" t="s">
+        <v>9</v>
+      </c>
+      <c r="J195" s="1">
+        <v>17</v>
+      </c>
+      <c r="K195" t="s">
+        <v>9</v>
+      </c>
+      <c r="L195" s="1">
+        <v>18</v>
+      </c>
+      <c r="M195" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A196" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B196" s="1">
+        <v>1</v>
+      </c>
+      <c r="C196" t="s">
+        <v>9</v>
+      </c>
+      <c r="D196" s="1">
+        <v>2</v>
+      </c>
+      <c r="E196" t="s">
+        <v>9</v>
+      </c>
+      <c r="F196" s="1">
+        <v>10</v>
+      </c>
+      <c r="G196" t="s">
+        <v>9</v>
+      </c>
+      <c r="H196" s="1">
+        <v>16</v>
+      </c>
+      <c r="I196" t="s">
+        <v>9</v>
+      </c>
+      <c r="J196" s="1">
+        <v>12</v>
+      </c>
+      <c r="K196" t="s">
+        <v>9</v>
+      </c>
+      <c r="L196" s="1">
+        <v>24</v>
+      </c>
+      <c r="M196" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A197" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B197" s="1">
+        <v>1</v>
+      </c>
+      <c r="C197" t="s">
+        <v>9</v>
+      </c>
+      <c r="D197" s="1">
+        <v>5</v>
+      </c>
+      <c r="E197" t="s">
+        <v>9</v>
+      </c>
+      <c r="F197" s="1">
+        <v>7</v>
+      </c>
+      <c r="G197" t="s">
+        <v>9</v>
+      </c>
+      <c r="H197" s="1">
+        <v>8</v>
+      </c>
+      <c r="I197" t="s">
+        <v>9</v>
+      </c>
+      <c r="J197" s="1">
+        <v>2</v>
+      </c>
+      <c r="K197" t="s">
+        <v>9</v>
+      </c>
+      <c r="L197" s="1">
+        <v>21</v>
+      </c>
+      <c r="M197" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A198" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B198" s="1">
+        <v>1</v>
+      </c>
+      <c r="C198" t="s">
+        <v>9</v>
+      </c>
+      <c r="D198" s="1">
+        <v>5</v>
+      </c>
+      <c r="E198" t="s">
+        <v>9</v>
+      </c>
+      <c r="F198" s="1">
+        <v>7</v>
+      </c>
+      <c r="G198" t="s">
+        <v>9</v>
+      </c>
+      <c r="H198" s="1">
+        <v>8</v>
+      </c>
+      <c r="I198" t="s">
+        <v>9</v>
+      </c>
+      <c r="J198" s="1">
+        <v>17</v>
+      </c>
+      <c r="K198" t="s">
+        <v>9</v>
+      </c>
+      <c r="L198" s="1">
+        <v>18</v>
+      </c>
+      <c r="M198" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A199" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B199" s="1">
+        <v>1</v>
+      </c>
+      <c r="C199" t="s">
+        <v>9</v>
+      </c>
+      <c r="D199" s="1">
+        <v>5</v>
+      </c>
+      <c r="E199" t="s">
+        <v>9</v>
+      </c>
+      <c r="F199" s="1">
+        <v>7</v>
+      </c>
+      <c r="G199" t="s">
+        <v>9</v>
+      </c>
+      <c r="H199" s="1">
+        <v>8</v>
+      </c>
+      <c r="I199" t="s">
+        <v>9</v>
+      </c>
+      <c r="J199" s="1">
+        <v>12</v>
+      </c>
+      <c r="K199" t="s">
+        <v>9</v>
+      </c>
+      <c r="L199" s="1">
+        <v>24</v>
+      </c>
+      <c r="M199" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
+</worksheet>
 </file>